--- a/Manual/source/CZ/tab/connectors.xlsx
+++ b/Manual/source/CZ/tab/connectors.xlsx
@@ -5,11 +5,19 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="X1_24V_5pin_BCZ" sheetId="1" state="visible" r:id="rId2"/>
     <sheet name="X2_48_DC_1778065" sheetId="2" state="visible" r:id="rId3"/>
+    <sheet name="X8_IO_22pin_BCZ" sheetId="3" state="visible" r:id="rId4"/>
+    <sheet name="X10_CAN_4pin_BCZ" sheetId="4" state="visible" r:id="rId5"/>
+    <sheet name="LEDsigAx12" sheetId="5" state="visible" r:id="rId6"/>
+    <sheet name="X5_FBE_12pin_BCZ" sheetId="6" state="visible" r:id="rId7"/>
+    <sheet name="X6_FB1_8pin_BCZ" sheetId="7" state="visible" r:id="rId8"/>
+    <sheet name="X7_FB2_8pin_BCZ" sheetId="8" state="visible" r:id="rId9"/>
+    <sheet name="X3_M1_6pin_BLZP" sheetId="9" state="visible" r:id="rId10"/>
+    <sheet name="X4_M2_6pin_BLZP" sheetId="10" state="visible" r:id="rId11"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -21,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="111">
   <si>
     <t xml:space="preserve">Pin č.</t>
   </si>
@@ -118,6 +126,279 @@
   <si>
     <t xml:space="preserve">0V (GND)</t>
   </si>
+  <si>
+    <t xml:space="preserve">AGND</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analogová (neoddělená) zem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0,14 – 1,5 mm2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AIN2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analogový vstup č. 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AIN1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analogový vstup č. 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DO6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Digitální výstup č. 6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DO5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Digitální výstup č. 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DO4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Digitální výstup č. 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DO3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Digitální výstup č. 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DO2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Digitální výstup č. 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DO1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Digitální výstup č. 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VCC DO2,4,6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Napájení DO 2,4,6 (osa 2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VCC DO1,3,5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Napájení DO 1,3,5 (osa 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DGND</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Digitální (oddělená) zem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DI8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Digitální vstup č. 8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DI7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Digitální vstup č. 7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DI6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Digitální vstup č. 6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DI5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Digitální vstup č. 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DI4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Digitální vstup č. 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DI3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Digitální vstup č. 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DI2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Digitální vstup č. 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DI1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Digitální vstup č. 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CANH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAN signál H</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CANL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAN signál L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CANGND</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAN oddělená zem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nepřipojeno</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barva LED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stav</t>
+  </si>
+  <si>
+    <t xml:space="preserve">zelená</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Servo OK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">červená</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Servo Error</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Endat 2.2/SSI/BISS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hiperface DSL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inkrementální enkodér</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+5 V</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+5V</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZERO-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N.C.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Z-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZERO+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Z+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FBSEL-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FBSEL+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DATA-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DATA+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLK-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLK+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DSL-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+12 V</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DSL+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- BRZDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0,2 ~ 4 mm2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+ BRZDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uzemnění</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fáze W</t>
+  </si>
+  <si>
+    <t xml:space="preserve">V</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fáze V</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fáze U</t>
+  </si>
 </sst>
 </file>
 
@@ -126,7 +407,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -154,6 +435,12 @@
     <font>
       <vertAlign val="superscript"/>
       <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="238"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="238"/>
@@ -201,9 +488,13 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -224,7 +515,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultColWidth="11.66015625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.66796875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="18.38"/>
@@ -319,6 +610,131 @@
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,obyčejné"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,obyčejné"&amp;12Stránka &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D18"/>
+  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="19.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="17.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="19.72"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>98</v>
+      </c>
+      <c r="C2" s="0" t="s">
+        <v>99</v>
+      </c>
+      <c r="D2" s="0" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>101</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>102</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>103</v>
+      </c>
+      <c r="C4" s="0" t="s">
+        <v>104</v>
+      </c>
+      <c r="D4" s="0" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>105</v>
+      </c>
+      <c r="C5" s="0" t="s">
+        <v>106</v>
+      </c>
+      <c r="D5" s="0" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>107</v>
+      </c>
+      <c r="C6" s="0" t="s">
+        <v>108</v>
+      </c>
+      <c r="D6" s="0" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>109</v>
+      </c>
+      <c r="C7" s="0" t="s">
+        <v>110</v>
+      </c>
+      <c r="D7" s="0" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C18" s="1"/>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,obyčejné"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,obyčejné"&amp;12Stránka &amp;P</oddFooter>
@@ -332,7 +748,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
@@ -375,6 +791,1130 @@
       <c r="D3" s="0" t="s">
         <v>17</v>
       </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,obyčejné"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,obyčejné"&amp;12Stránka &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D23"/>
+  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="30.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="19.72"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="D11" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="D12" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="D13" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="D14" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="C15" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="D15" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="0" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="D16" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="C17" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="D17" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="0" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="C18" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="D18" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="C19" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="D19" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="C20" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="D20" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="C21" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="D21" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="0" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="0" t="s">
+        <v>57</v>
+      </c>
+      <c r="C22" s="0" t="s">
+        <v>58</v>
+      </c>
+      <c r="D22" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="C23" s="0" t="s">
+        <v>60</v>
+      </c>
+      <c r="D23" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,obyčejné"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,obyčejné"&amp;12Stránka &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="17.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="18.33"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="C2" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="C4" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="D4" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="C5" s="0" t="s">
+        <v>68</v>
+      </c>
+      <c r="D5" s="0" t="s">
+        <v>22</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,obyčejné"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,obyčejné"&amp;12Stránka &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14.63"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
+        <v>69</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
+        <v>71</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>74</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,obyčejné"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,obyčejné"&amp;12Stránka &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D18"/>
+  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="19.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="17.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="19.72"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>75</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>78</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="C4" s="0" t="s">
+        <v>81</v>
+      </c>
+      <c r="D4" s="0" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>83</v>
+      </c>
+      <c r="C5" s="0" t="s">
+        <v>81</v>
+      </c>
+      <c r="D5" s="0" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>81</v>
+      </c>
+      <c r="C6" s="0" t="s">
+        <v>85</v>
+      </c>
+      <c r="D6" s="0" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>81</v>
+      </c>
+      <c r="C7" s="0" t="s">
+        <v>86</v>
+      </c>
+      <c r="D7" s="0" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>87</v>
+      </c>
+      <c r="C8" s="0" t="s">
+        <v>85</v>
+      </c>
+      <c r="D8" s="0" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="0" t="s">
+        <v>89</v>
+      </c>
+      <c r="C9" s="0" t="s">
+        <v>86</v>
+      </c>
+      <c r="D9" s="0" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="0" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10" s="0" t="s">
+        <v>81</v>
+      </c>
+      <c r="D10" s="0" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="0" t="s">
+        <v>93</v>
+      </c>
+      <c r="C11" s="0" t="s">
+        <v>81</v>
+      </c>
+      <c r="D11" s="0" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" s="0" t="s">
+        <v>95</v>
+      </c>
+      <c r="D12" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="0" t="s">
+        <v>96</v>
+      </c>
+      <c r="C13" s="0" t="s">
+        <v>97</v>
+      </c>
+      <c r="D13" s="0" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C18" s="1"/>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,obyčejné"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,obyčejné"&amp;12Stránka &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D18"/>
+  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="19.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="17.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="19.72"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>75</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>81</v>
+      </c>
+      <c r="C2" s="0" t="s">
+        <v>85</v>
+      </c>
+      <c r="D2" s="0" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>81</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>86</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>87</v>
+      </c>
+      <c r="C4" s="0" t="s">
+        <v>85</v>
+      </c>
+      <c r="D4" s="0" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>89</v>
+      </c>
+      <c r="C5" s="0" t="s">
+        <v>86</v>
+      </c>
+      <c r="D5" s="0" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6" s="0" t="s">
+        <v>81</v>
+      </c>
+      <c r="D6" s="0" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>93</v>
+      </c>
+      <c r="C7" s="0" t="s">
+        <v>81</v>
+      </c>
+      <c r="D7" s="0" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="0" t="s">
+        <v>95</v>
+      </c>
+      <c r="D8" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="0" t="s">
+        <v>96</v>
+      </c>
+      <c r="C9" s="0" t="s">
+        <v>97</v>
+      </c>
+      <c r="D9" s="0" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C18" s="1"/>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,obyčejné"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,obyčejné"&amp;12Stránka &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D18"/>
+  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="19.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="17.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="19.72"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>75</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>81</v>
+      </c>
+      <c r="C2" s="0" t="s">
+        <v>85</v>
+      </c>
+      <c r="D2" s="0" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>81</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>86</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>87</v>
+      </c>
+      <c r="C4" s="0" t="s">
+        <v>85</v>
+      </c>
+      <c r="D4" s="0" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>89</v>
+      </c>
+      <c r="C5" s="0" t="s">
+        <v>86</v>
+      </c>
+      <c r="D5" s="0" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6" s="0" t="s">
+        <v>81</v>
+      </c>
+      <c r="D6" s="0" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>93</v>
+      </c>
+      <c r="C7" s="0" t="s">
+        <v>81</v>
+      </c>
+      <c r="D7" s="0" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="0" t="s">
+        <v>95</v>
+      </c>
+      <c r="D8" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="0" t="s">
+        <v>96</v>
+      </c>
+      <c r="C9" s="0" t="s">
+        <v>97</v>
+      </c>
+      <c r="D9" s="0" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C18" s="1"/>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,obyčejné"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,obyčejné"&amp;12Stránka &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D18"/>
+  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="19.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="17.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="19.72"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>98</v>
+      </c>
+      <c r="C2" s="0" t="s">
+        <v>99</v>
+      </c>
+      <c r="D2" s="0" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>101</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>102</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>103</v>
+      </c>
+      <c r="C4" s="0" t="s">
+        <v>104</v>
+      </c>
+      <c r="D4" s="0" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>105</v>
+      </c>
+      <c r="C5" s="0" t="s">
+        <v>106</v>
+      </c>
+      <c r="D5" s="0" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>107</v>
+      </c>
+      <c r="C6" s="0" t="s">
+        <v>108</v>
+      </c>
+      <c r="D6" s="0" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>109</v>
+      </c>
+      <c r="C7" s="0" t="s">
+        <v>110</v>
+      </c>
+      <c r="D7" s="0" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C18" s="1"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/Manual/source/CZ/tab/connectors.xlsx
+++ b/Manual/source/CZ/tab/connectors.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="9"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="12"/>
   </bookViews>
   <sheets>
     <sheet name="X1_24V_5pin_BCZ" sheetId="1" state="visible" r:id="rId2"/>
@@ -18,6 +18,10 @@
     <sheet name="X7_FB2_8pin_BCZ" sheetId="8" state="visible" r:id="rId9"/>
     <sheet name="X3_M1_6pin_BLZP" sheetId="9" state="visible" r:id="rId10"/>
     <sheet name="X4_M2_6pin_BLZP" sheetId="10" state="visible" r:id="rId11"/>
+    <sheet name="X1_24V_5pin_Microlock" sheetId="11" state="visible" r:id="rId12"/>
+    <sheet name="X3_DCbus_2pin_pressfit" sheetId="12" state="visible" r:id="rId13"/>
+    <sheet name="X3_M1_3pin_pressfit" sheetId="13" state="visible" r:id="rId14"/>
+    <sheet name="X4_BR_4pin_Microlock" sheetId="14" state="visible" r:id="rId15"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -29,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="125">
   <si>
     <t xml:space="preserve">Pin č.</t>
   </si>
@@ -398,6 +402,48 @@
   </si>
   <si>
     <t xml:space="preserve">Fáze U</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0,13 ~ 0,32 mm2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Připojení</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 V</t>
+  </si>
+  <si>
+    <t xml:space="preserve">oko M5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+6 ~ +50 V</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fáze W</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fáze V</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fáze U</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-BR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+BR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-TERM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Tepl. čidla mot.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+TERM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+ Tepl. čidla mot.</t>
   </si>
 </sst>
 </file>
@@ -515,7 +561,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultColWidth="11.66796875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.6875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="18.38"/>
@@ -623,7 +669,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D18"/>
-  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="19.31"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="17.78"/>
@@ -735,6 +781,360 @@
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,obyčejné"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,obyčejné"&amp;12Stránka &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultColWidth="11.6875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="18.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12.83"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="0" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="0" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="0" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="0" t="s">
+        <v>111</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,obyčejné"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,obyčejné"&amp;12Stránka &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D18"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="19.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="17.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="19.72"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="0" t="s">
+        <v>113</v>
+      </c>
+      <c r="D2" s="0" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>115</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C18" s="1"/>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,obyčejné"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,obyčejné"&amp;12Stránka &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D18"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="19.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="17.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="19.72"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>105</v>
+      </c>
+      <c r="C2" s="0" t="s">
+        <v>116</v>
+      </c>
+      <c r="D2" s="0" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>107</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>117</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>109</v>
+      </c>
+      <c r="C4" s="0" t="s">
+        <v>118</v>
+      </c>
+      <c r="D4" s="0" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C18" s="1"/>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,obyčejné"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,obyčejné"&amp;12Stránka &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultColWidth="11.6875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="18.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12.83"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>119</v>
+      </c>
+      <c r="C2" s="0" t="s">
+        <v>99</v>
+      </c>
+      <c r="D2" s="0" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>120</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>102</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>121</v>
+      </c>
+      <c r="C4" s="0" t="s">
+        <v>122</v>
+      </c>
+      <c r="D4" s="0" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>123</v>
+      </c>
+      <c r="C5" s="0" t="s">
+        <v>124</v>
+      </c>
+      <c r="D5" s="0" t="s">
+        <v>111</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,obyčejné"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,obyčejné"&amp;12Stránka &amp;P</oddFooter>
@@ -748,7 +1148,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
@@ -809,7 +1209,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D23"/>
-  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="30.7"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="19.72"/>
@@ -1154,7 +1554,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="17.09"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="18.33"/>
@@ -1247,9 +1647,9 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14.62"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1293,7 +1693,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D18"/>
-  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="19.31"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="17.78"/>
@@ -1502,7 +1902,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D18"/>
-  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="19.31"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="17.78"/>
@@ -1655,7 +2055,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D18"/>
-  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="19.31"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="17.78"/>
@@ -1808,7 +2208,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D18"/>
-  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="19.31"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="17.78"/>

--- a/Manual/source/CZ/tab/connectors.xlsx
+++ b/Manual/source/CZ/tab/connectors.xlsx
@@ -5,23 +5,24 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="12"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="X1_24V_5pin_BCZ" sheetId="1" state="visible" r:id="rId2"/>
-    <sheet name="X2_48_DC_1778065" sheetId="2" state="visible" r:id="rId3"/>
-    <sheet name="X8_IO_22pin_BCZ" sheetId="3" state="visible" r:id="rId4"/>
-    <sheet name="X10_CAN_4pin_BCZ" sheetId="4" state="visible" r:id="rId5"/>
-    <sheet name="LEDsigAx12" sheetId="5" state="visible" r:id="rId6"/>
-    <sheet name="X5_FBE_12pin_BCZ" sheetId="6" state="visible" r:id="rId7"/>
-    <sheet name="X6_FB1_8pin_BCZ" sheetId="7" state="visible" r:id="rId8"/>
-    <sheet name="X7_FB2_8pin_BCZ" sheetId="8" state="visible" r:id="rId9"/>
-    <sheet name="X3_M1_6pin_BLZP" sheetId="9" state="visible" r:id="rId10"/>
-    <sheet name="X4_M2_6pin_BLZP" sheetId="10" state="visible" r:id="rId11"/>
-    <sheet name="X1_24V_5pin_Microlock" sheetId="11" state="visible" r:id="rId12"/>
-    <sheet name="X3_DCbus_2pin_pressfit" sheetId="12" state="visible" r:id="rId13"/>
-    <sheet name="X3_M1_3pin_pressfit" sheetId="13" state="visible" r:id="rId14"/>
-    <sheet name="X4_BR_4pin_Microlock" sheetId="14" state="visible" r:id="rId15"/>
+    <sheet name="rozcestnik" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="X1_24V_5pin_BCZ" sheetId="2" state="visible" r:id="rId3"/>
+    <sheet name="X2_48_DC_1778065" sheetId="3" state="visible" r:id="rId4"/>
+    <sheet name="X8_IO_22pin_BCZ" sheetId="4" state="visible" r:id="rId5"/>
+    <sheet name="X10_CAN_4pin_BCZ" sheetId="5" state="visible" r:id="rId6"/>
+    <sheet name="LEDsigAx12" sheetId="6" state="visible" r:id="rId7"/>
+    <sheet name="X5_FBE_12pin_BCZ" sheetId="7" state="visible" r:id="rId8"/>
+    <sheet name="X6_FB1_8pin_BCZ" sheetId="8" state="visible" r:id="rId9"/>
+    <sheet name="X7_FB2_8pin_BCZ" sheetId="9" state="visible" r:id="rId10"/>
+    <sheet name="X3_M1_6pin_BLZP" sheetId="10" state="visible" r:id="rId11"/>
+    <sheet name="X4_M2_6pin_BLZP" sheetId="11" state="visible" r:id="rId12"/>
+    <sheet name="X1_24V_5pin_Microlock" sheetId="12" state="visible" r:id="rId13"/>
+    <sheet name="X3_DCbus_2pin_pressfit" sheetId="13" state="visible" r:id="rId14"/>
+    <sheet name="X3_M1_3pin_pressfit" sheetId="14" state="visible" r:id="rId15"/>
+    <sheet name="X4_BR_4pin_Microlock" sheetId="15" state="visible" r:id="rId16"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -33,7 +34,91 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="153">
+  <si>
+    <t xml:space="preserve">Toto je sešit se zdrojovými tabulkami popisu konektorů TGZ/TGS v češtině. Každý list odpovídá jednomu unikátnímu typu konektoru. Jelikož se často konektory v rámci TGZ opakují (typicky ty na řídicií desce), jsou zde jen jednou. Tj. Např. IO konektor 22pin weidmuller BCZ se používá pořád dokola, je zde tedy zanesen jen jednou jako „X8_IO_22pin_BCZ“</t>
+  </si>
+  <si>
+    <t xml:space="preserve">výrobce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">řada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">počet OS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">napětí</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jmen. Proud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">špičkový proud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">typ konektoru</t>
+  </si>
+  <si>
+    <t xml:space="preserve">list</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TGZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24V</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#X1_24V_5pin_Microlock</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#X8_IO_22pin_BCZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#X10_CAN_4pin_BCZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FB1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#X6_FB1_8pin_BCZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FB2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#X7_FB2_8pin_BCZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FBE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#X5_FBE_12pin_BCZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#X3_M1_3pin_pressfit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dcbus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#X3_DCbus_2pin_pressfit</t>
+  </si>
   <si>
     <t xml:space="preserve">Pin č.</t>
   </si>
@@ -453,7 +538,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -479,6 +564,13 @@
       <charset val="238"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="238"/>
+    </font>
+    <font>
       <vertAlign val="superscript"/>
       <sz val="10"/>
       <name val="Arial"/>
@@ -492,12 +584,18 @@
       <charset val="238"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF5CE"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -534,12 +632,28 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -552,6 +666,66 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FFC0C0C0"/>
+      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFFFF5CE"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FF660066"/>
+      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -560,99 +734,252 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultColWidth="11.6875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:H17"/>
+  <sheetFormatPr defaultColWidth="12.23828125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="18.38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="13.8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="14.59"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="31.81"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="B8" s="0" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="C8" s="0" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="0" t="s">
+      <c r="D8" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="E8" s="0" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="F8" s="0" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="0" t="s">
+      <c r="G8" s="0" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="H8" s="0" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="0" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="0" t="s">
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="B9" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="0" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="0" t="s">
+      <c r="C9" s="0" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="D9" s="0" t="n">
+        <v>48</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="G9" s="0" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="0" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="0" t="s">
+      <c r="H9" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="0" t="s">
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C10" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" s="0" t="n">
+        <v>48</v>
+      </c>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="0" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="0" t="s">
-        <v>6</v>
+      <c r="H10" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C11" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="0" t="n">
+        <v>48</v>
+      </c>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D12" s="0" t="n">
+        <v>48</v>
+      </c>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D13" s="0" t="n">
+        <v>48</v>
+      </c>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D14" s="0" t="n">
+        <v>48</v>
+      </c>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D15" s="0" t="n">
+        <v>48</v>
+      </c>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D16" s="0" t="n">
+        <v>48</v>
+      </c>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D17" s="0" t="n">
+        <v>48</v>
+      </c>
+      <c r="E17" s="0" t="n">
+        <v>100</v>
+      </c>
+      <c r="F17" s="0" t="n">
+        <v>250</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:H6"/>
+    <mergeCell ref="E9:E16"/>
+    <mergeCell ref="F9:F16"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="H9" location="X1_24V_5pin_Microlock!A1" display="#X1_24V_5pin_Microlock"/>
+    <hyperlink ref="H10" location="X8_IO_22pin_BCZ!A1" display="#X8_IO_22pin_BCZ"/>
+    <hyperlink ref="H11" location="X10_CAN_4pin_BCZ!A1" display="#X10_CAN_4pin_BCZ"/>
+    <hyperlink ref="H12" location="X6_FB1_8pin_BCZ!A1" display="#X6_FB1_8pin_BCZ"/>
+    <hyperlink ref="H13" location="X7_FB2_8pin_BCZ!A1" display="#X7_FB2_8pin_BCZ"/>
+    <hyperlink ref="H14" location="X5_FBE_12pin_BCZ!A1" display="#X5_FBE_12pin_BCZ"/>
+    <hyperlink ref="H15" location="X3_M1_3pin_pressfit!A1" display="#X3_M1_3pin_pressfit"/>
+    <hyperlink ref="H16" location="X3_DCbus_2pin_pressfit!A1" display="#X3_DCbus_2pin_pressfit"/>
+  </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -678,16 +1005,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>3</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -695,13 +1022,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>98</v>
+        <v>126</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>99</v>
+        <v>127</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>100</v>
+        <v>128</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -709,13 +1036,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>101</v>
+        <v>129</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>102</v>
+        <v>130</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>100</v>
+        <v>128</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -723,13 +1050,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>103</v>
+        <v>131</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>104</v>
+        <v>132</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>100</v>
+        <v>128</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -737,13 +1064,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>105</v>
+        <v>133</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>106</v>
+        <v>134</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>100</v>
+        <v>128</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -751,13 +1078,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>107</v>
+        <v>135</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>108</v>
+        <v>136</v>
       </c>
       <c r="D6" s="0" t="s">
-        <v>100</v>
+        <v>128</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -765,17 +1092,17 @@
         <v>6</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>109</v>
+        <v>137</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>110</v>
+        <v>138</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>100</v>
+        <v>128</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C18" s="1"/>
+      <c r="C18" s="5"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -793,26 +1120,26 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultColWidth="11.6875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:D18"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="18.38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="19.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="17.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="19.72"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>3</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -820,13 +1147,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>4</v>
+        <v>126</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>5</v>
+        <v>127</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>111</v>
+        <v>128</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -834,13 +1161,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>7</v>
+        <v>129</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>8</v>
+        <v>130</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>111</v>
+        <v>128</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -848,13 +1175,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>9</v>
+        <v>131</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>10</v>
+        <v>132</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>111</v>
+        <v>128</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -862,13 +1189,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>11</v>
+        <v>133</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>12</v>
+        <v>134</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>111</v>
+        <v>128</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -876,19 +1203,36 @@
         <v>5</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>13</v>
+        <v>135</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>14</v>
+        <v>136</v>
       </c>
       <c r="D6" s="0" t="s">
-        <v>111</v>
-      </c>
+        <v>128</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>137</v>
+      </c>
+      <c r="C7" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="D7" s="0" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C18" s="5"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,obyčejné"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,obyčejné"&amp;12Stránka &amp;P</oddFooter>
@@ -901,26 +1245,26 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultColWidth="11.6875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="19.31"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="17.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="19.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="18.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12.83"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>112</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -928,13 +1272,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>113</v>
+        <v>33</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>114</v>
+        <v>139</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -942,22 +1286,61 @@
         <v>2</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>115</v>
+        <v>36</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C18" s="1"/>
+        <v>139</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4" s="0" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="D5" s="0" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6" s="0" t="s">
+        <v>139</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;"Times New Roman,obyčejné"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,obyčejné"&amp;12Stránka &amp;P</oddFooter>
@@ -980,62 +1363,48 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>112</v>
+        <v>140</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>105</v>
+        <v>46</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>116</v>
+        <v>141</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>114</v>
+        <v>142</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>107</v>
+        <v>43</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>117</v>
+        <v>143</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="B4" s="0" t="s">
-        <v>109</v>
-      </c>
-      <c r="C4" s="0" t="s">
-        <v>118</v>
-      </c>
-      <c r="D4" s="0" t="s">
-        <v>114</v>
+        <v>142</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C18" s="1"/>
+      <c r="C18" s="5"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -1053,6 +1422,89 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:D18"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="19.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="17.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="19.72"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>133</v>
+      </c>
+      <c r="C2" s="0" t="s">
+        <v>144</v>
+      </c>
+      <c r="D2" s="0" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>145</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>137</v>
+      </c>
+      <c r="C4" s="0" t="s">
+        <v>146</v>
+      </c>
+      <c r="D4" s="0" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C18" s="5"/>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,obyčejné"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,obyčejné"&amp;12Stránka &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:D5"/>
   <sheetFormatPr defaultColWidth="11.6875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -1063,16 +1515,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>3</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1080,13 +1532,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>119</v>
+        <v>147</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>99</v>
+        <v>127</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>111</v>
+        <v>139</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1094,13 +1546,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>120</v>
+        <v>148</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>102</v>
+        <v>130</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>111</v>
+        <v>139</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1108,13 +1560,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>121</v>
+        <v>149</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>122</v>
+        <v>150</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>111</v>
+        <v>139</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1122,13 +1574,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>123</v>
+        <v>151</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>124</v>
+        <v>152</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>111</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>
@@ -1147,21 +1599,26 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultColWidth="11.6875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="18.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12.83"/>
+  </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>3</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1169,13 +1626,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1183,13 +1640,55 @@
         <v>2</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>17</v>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4" s="0" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="D5" s="0" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6" s="0" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -1208,25 +1707,21 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="30.7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="19.72"/>
-  </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>3</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1234,13 +1729,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1248,293 +1743,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" s="0" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" s="0" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="C6" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="D6" s="0" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="C7" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="D7" s="0" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="C8" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="D8" s="0" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="C9" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="D9" s="0" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="C10" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="D10" s="0" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="C11" s="0" t="s">
-        <v>38</v>
-      </c>
-      <c r="D11" s="0" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="0" t="s">
-        <v>39</v>
-      </c>
-      <c r="C12" s="0" t="s">
-        <v>40</v>
-      </c>
-      <c r="D12" s="0" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="0" t="s">
-        <v>41</v>
-      </c>
-      <c r="C13" s="0" t="s">
-        <v>42</v>
-      </c>
-      <c r="D13" s="0" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="0" t="s">
-        <v>43</v>
-      </c>
-      <c r="C14" s="0" t="s">
-        <v>44</v>
-      </c>
-      <c r="D14" s="0" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="0" t="s">
-        <v>43</v>
-      </c>
-      <c r="C15" s="0" t="s">
-        <v>44</v>
-      </c>
-      <c r="D15" s="0" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="0" t="s">
         <v>45</v>
-      </c>
-      <c r="C16" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="D16" s="0" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="C17" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="D17" s="0" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="C18" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="D18" s="0" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="0" t="s">
-        <v>51</v>
-      </c>
-      <c r="C19" s="0" t="s">
-        <v>52</v>
-      </c>
-      <c r="D19" s="0" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" s="0" t="s">
-        <v>53</v>
-      </c>
-      <c r="C20" s="0" t="s">
-        <v>54</v>
-      </c>
-      <c r="D20" s="0" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" s="0" t="s">
-        <v>55</v>
-      </c>
-      <c r="C21" s="0" t="s">
-        <v>56</v>
-      </c>
-      <c r="D21" s="0" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" s="0" t="s">
-        <v>57</v>
-      </c>
-      <c r="C22" s="0" t="s">
-        <v>58</v>
-      </c>
-      <c r="D22" s="0" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="C23" s="0" t="s">
-        <v>60</v>
-      </c>
-      <c r="D23" s="0" t="s">
-        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -1553,25 +1768,25 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="17.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="18.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="30.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="19.72"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>3</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1579,13 +1794,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1593,13 +1808,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1607,13 +1822,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1621,13 +1836,265 @@
         <v>4</v>
       </c>
       <c r="B5" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="C5" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="D5" s="0" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="C6" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="D6" s="0" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>57</v>
+      </c>
+      <c r="C7" s="0" t="s">
+        <v>58</v>
+      </c>
+      <c r="D7" s="0" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="C8" s="0" t="s">
+        <v>60</v>
+      </c>
+      <c r="D8" s="0" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="C9" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="D9" s="0" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="C10" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="D10" s="0" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="C11" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="D11" s="0" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="0" t="s">
         <v>67</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C12" s="0" t="s">
         <v>68</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D12" s="0" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="0" t="s">
+        <v>69</v>
+      </c>
+      <c r="C13" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="D13" s="0" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="0" t="s">
+        <v>71</v>
+      </c>
+      <c r="C14" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="D14" s="0" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="0" t="s">
+        <v>71</v>
+      </c>
+      <c r="C15" s="0" t="s">
+        <v>72</v>
+      </c>
+      <c r="D15" s="0" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="C16" s="0" t="s">
+        <v>74</v>
+      </c>
+      <c r="D16" s="0" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="0" t="s">
+        <v>75</v>
+      </c>
+      <c r="C17" s="0" t="s">
+        <v>76</v>
+      </c>
+      <c r="D17" s="0" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="0" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="0" t="s">
+        <v>77</v>
+      </c>
+      <c r="C18" s="0" t="s">
+        <v>78</v>
+      </c>
+      <c r="D18" s="0" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="0" t="s">
+        <v>79</v>
+      </c>
+      <c r="C19" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="D19" s="0" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="0" t="s">
+        <v>81</v>
+      </c>
+      <c r="C20" s="0" t="s">
+        <v>82</v>
+      </c>
+      <c r="D20" s="0" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="0" t="s">
+        <v>83</v>
+      </c>
+      <c r="C21" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="D21" s="0" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="0" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="0" t="s">
+        <v>85</v>
+      </c>
+      <c r="C22" s="0" t="s">
+        <v>86</v>
+      </c>
+      <c r="D22" s="0" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="0" t="n">
         <v>22</v>
+      </c>
+      <c r="B23" s="0" t="s">
+        <v>87</v>
+      </c>
+      <c r="C23" s="0" t="s">
+        <v>88</v>
+      </c>
+      <c r="D23" s="0" t="s">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -1646,34 +2113,81 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14.62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="17.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="18.33"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>69</v>
+        <v>28</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>70</v>
+        <v>29</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
-        <v>71</v>
+      <c r="A2" s="0" t="n">
+        <v>1</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>72</v>
+        <v>89</v>
+      </c>
+      <c r="C2" s="0" t="s">
+        <v>90</v>
+      </c>
+      <c r="D2" s="0" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
-        <v>73</v>
+      <c r="A3" s="0" t="n">
+        <v>2</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>74</v>
+        <v>91</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>92</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>93</v>
+      </c>
+      <c r="C4" s="0" t="s">
+        <v>94</v>
+      </c>
+      <c r="D4" s="0" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>95</v>
+      </c>
+      <c r="C5" s="0" t="s">
+        <v>96</v>
+      </c>
+      <c r="D5" s="0" t="s">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -1692,198 +2206,35 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="19.31"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="17.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="19.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14.62"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>75</v>
-      </c>
-      <c r="C1" s="0" t="s">
-        <v>76</v>
-      </c>
-      <c r="D1" s="0" t="s">
-        <v>77</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
-        <v>1</v>
+      <c r="A2" s="0" t="s">
+        <v>99</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" s="0" t="s">
-        <v>13</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
-        <v>2</v>
+      <c r="A3" s="0" t="s">
+        <v>101</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>78</v>
-      </c>
-      <c r="C3" s="0" t="s">
-        <v>79</v>
-      </c>
-      <c r="D3" s="0" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="0" t="s">
-        <v>80</v>
-      </c>
-      <c r="C4" s="0" t="s">
-        <v>81</v>
-      </c>
-      <c r="D4" s="0" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="0" t="s">
-        <v>83</v>
-      </c>
-      <c r="C5" s="0" t="s">
-        <v>81</v>
-      </c>
-      <c r="D5" s="0" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="0" t="s">
-        <v>81</v>
-      </c>
-      <c r="C6" s="0" t="s">
-        <v>85</v>
-      </c>
-      <c r="D6" s="0" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="0" t="s">
-        <v>81</v>
-      </c>
-      <c r="C7" s="0" t="s">
-        <v>86</v>
-      </c>
-      <c r="D7" s="0" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="0" t="s">
-        <v>87</v>
-      </c>
-      <c r="C8" s="0" t="s">
-        <v>85</v>
-      </c>
-      <c r="D8" s="0" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="0" t="s">
-        <v>89</v>
-      </c>
-      <c r="C9" s="0" t="s">
-        <v>86</v>
-      </c>
-      <c r="D9" s="0" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="0" t="s">
-        <v>91</v>
-      </c>
-      <c r="C10" s="0" t="s">
-        <v>81</v>
-      </c>
-      <c r="D10" s="0" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="0" t="s">
-        <v>93</v>
-      </c>
-      <c r="C11" s="0" t="s">
-        <v>81</v>
-      </c>
-      <c r="D11" s="0" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="C12" s="0" t="s">
-        <v>95</v>
-      </c>
-      <c r="D12" s="0" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="0" t="s">
-        <v>96</v>
-      </c>
-      <c r="C13" s="0" t="s">
-        <v>97</v>
-      </c>
-      <c r="D13" s="0" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C18" s="1"/>
+        <v>102</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -1911,16 +2262,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>75</v>
+        <v>103</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>77</v>
+        <v>105</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1928,13 +2279,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>81</v>
+        <v>41</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>85</v>
+        <v>41</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>81</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1942,13 +2293,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>81</v>
+        <v>106</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>81</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1956,13 +2307,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>85</v>
+        <v>109</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>88</v>
+        <v>110</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1970,13 +2321,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>89</v>
+        <v>111</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>86</v>
+        <v>109</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1984,13 +2335,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>81</v>
+        <v>113</v>
       </c>
       <c r="D6" s="0" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1998,13 +2349,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>81</v>
+        <v>114</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>94</v>
+        <v>109</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2012,13 +2363,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>13</v>
+        <v>115</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>95</v>
+        <v>113</v>
       </c>
       <c r="D8" s="0" t="s">
-        <v>13</v>
+        <v>116</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2026,17 +2377,73 @@
         <v>8</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>96</v>
+        <v>117</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="D9" s="0" t="s">
-        <v>96</v>
+        <v>118</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="0" t="s">
+        <v>119</v>
+      </c>
+      <c r="C10" s="0" t="s">
+        <v>109</v>
+      </c>
+      <c r="D10" s="0" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="0" t="s">
+        <v>121</v>
+      </c>
+      <c r="C11" s="0" t="s">
+        <v>109</v>
+      </c>
+      <c r="D11" s="0" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" s="0" t="s">
+        <v>123</v>
+      </c>
+      <c r="D12" s="0" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="0" t="s">
+        <v>124</v>
+      </c>
+      <c r="C13" s="0" t="s">
+        <v>125</v>
+      </c>
+      <c r="D13" s="0" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C18" s="1"/>
+      <c r="C18" s="5"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -2064,16 +2471,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>75</v>
+        <v>103</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>77</v>
+        <v>105</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2081,13 +2488,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>85</v>
+        <v>113</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>81</v>
+        <v>109</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2095,13 +2502,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>86</v>
+        <v>114</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>81</v>
+        <v>109</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2109,13 +2516,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>87</v>
+        <v>115</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>85</v>
+        <v>113</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>88</v>
+        <v>116</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2123,13 +2530,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>89</v>
+        <v>117</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>86</v>
+        <v>114</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>90</v>
+        <v>118</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2137,13 +2544,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>91</v>
+        <v>119</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="D6" s="0" t="s">
-        <v>92</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2151,13 +2558,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>93</v>
+        <v>121</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>94</v>
+        <v>122</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2165,13 +2572,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>95</v>
+        <v>123</v>
       </c>
       <c r="D8" s="0" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2179,17 +2586,17 @@
         <v>8</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>96</v>
+        <v>124</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>97</v>
+        <v>125</v>
       </c>
       <c r="D9" s="0" t="s">
-        <v>96</v>
+        <v>124</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C18" s="1"/>
+      <c r="C18" s="5"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -2217,16 +2624,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>1</v>
+        <v>103</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>2</v>
+        <v>104</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>3</v>
+        <v>105</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2234,13 +2641,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2248,13 +2655,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2262,13 +2669,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>100</v>
+        <v>116</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2276,13 +2683,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>100</v>
+        <v>118</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2290,13 +2697,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D6" s="0" t="s">
-        <v>100</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2304,17 +2711,45 @@
         <v>6</v>
       </c>
       <c r="B7" s="0" t="s">
+        <v>121</v>
+      </c>
+      <c r="C7" s="0" t="s">
         <v>109</v>
       </c>
-      <c r="C7" s="0" t="s">
-        <v>110</v>
-      </c>
       <c r="D7" s="0" t="s">
-        <v>100</v>
+        <v>122</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" s="0" t="s">
+        <v>123</v>
+      </c>
+      <c r="D8" s="0" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="0" t="s">
+        <v>124</v>
+      </c>
+      <c r="C9" s="0" t="s">
+        <v>125</v>
+      </c>
+      <c r="D9" s="0" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C18" s="1"/>
+      <c r="C18" s="5"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/Manual/source/CZ/tab/connectors.xlsx
+++ b/Manual/source/CZ/tab/connectors.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="22"/>
   </bookViews>
   <sheets>
     <sheet name="rozcestnik" sheetId="1" state="visible" r:id="rId2"/>
@@ -23,6 +23,14 @@
     <sheet name="X3_DCbus_2pin_pressfit" sheetId="13" state="visible" r:id="rId14"/>
     <sheet name="X3_M1_3pin_pressfit" sheetId="14" state="visible" r:id="rId15"/>
     <sheet name="X4_BR_4pin_Microlock" sheetId="15" state="visible" r:id="rId16"/>
+    <sheet name="X2_DCbus_3pin_wago_2636" sheetId="16" state="visible" r:id="rId17"/>
+    <sheet name="X3_M1_4pin_wago_2626" sheetId="17" state="visible" r:id="rId18"/>
+    <sheet name="X4_M2_4pin_wago_2626" sheetId="18" state="visible" r:id="rId19"/>
+    <sheet name="XBR_BR_6pin_BLF" sheetId="19" state="visible" r:id="rId20"/>
+    <sheet name="X1_24V_5pin_Microfit" sheetId="20" state="visible" r:id="rId21"/>
+    <sheet name="P7_BR_4pin_Microfit" sheetId="21" state="visible" r:id="rId22"/>
+    <sheet name="P8_BR_4pin_Microfit" sheetId="22" state="visible" r:id="rId23"/>
+    <sheet name="P3_Term_2pin_Microfit" sheetId="23" state="visible" r:id="rId24"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -34,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="179">
   <si>
     <t xml:space="preserve">Toto je sešit se zdrojovými tabulkami popisu konektorů TGZ/TGS v češtině. Každý list odpovídá jednomu unikátnímu typu konektoru. Jelikož se často konektory v rámci TGZ opakují (typicky ty na řídicií desce), jsou zde jen jednou. Tj. Např. IO konektor 22pin weidmuller BCZ se používá pořád dokola, je zde tedy zanesen jen jednou jako „X8_IO_22pin_BCZ“</t>
   </si>
@@ -530,13 +538,92 @@
   <si>
     <t xml:space="preserve">+ Tepl. čidla mot.</t>
   </si>
+  <si>
+    <t xml:space="preserve">uzemnění</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0,75 ~ 16 mm2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0,2 ~ 10 mm2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-B2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Brzda motor 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0,13 ~ 2,5 mm2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+ Brzda motor 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">– Napájení brzdy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+ Napájení brzdy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-B1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Brzda motor 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+B1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+ Brzda motor 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+24V DC napájení řízení</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0,05 ~ 0,75 mm2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VCC_OUT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Výstup +24 VDC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+24V DC napájení brzdy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VCCD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+24V DC napájení diag. brzdy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+ Brzda servomotoru</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Brzda servomotoru</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nezapojuje se</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0V napájení řízení</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TERM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teplotní čidlo PT1000</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="@"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -632,7 +719,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -655,6 +742,10 @@
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1594,6 +1685,409 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D18"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="19.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="17.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="19.72"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>131</v>
+      </c>
+      <c r="C2" s="0" t="s">
+        <v>153</v>
+      </c>
+      <c r="D2" s="0" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>141</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="C4" s="0" t="s">
+        <v>143</v>
+      </c>
+      <c r="D4" s="0" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C18" s="5"/>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,obyčejné"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,obyčejné"&amp;12Stránka &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D18"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="19.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="17.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="19.72"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>131</v>
+      </c>
+      <c r="C2" s="0" t="s">
+        <v>153</v>
+      </c>
+      <c r="D2" s="0" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>133</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>144</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="C4" s="0" t="s">
+        <v>145</v>
+      </c>
+      <c r="D4" s="0" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>137</v>
+      </c>
+      <c r="C5" s="0" t="s">
+        <v>146</v>
+      </c>
+      <c r="D5" s="0" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C18" s="5"/>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,obyčejné"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,obyčejné"&amp;12Stránka &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D18"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="19.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="17.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="19.72"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>131</v>
+      </c>
+      <c r="C2" s="0" t="s">
+        <v>153</v>
+      </c>
+      <c r="D2" s="0" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>133</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>144</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="C4" s="0" t="s">
+        <v>145</v>
+      </c>
+      <c r="D4" s="0" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>137</v>
+      </c>
+      <c r="C5" s="0" t="s">
+        <v>146</v>
+      </c>
+      <c r="D5" s="0" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C18" s="5"/>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,obyčejné"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,obyčejné"&amp;12Stránka &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D18"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="19.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="27.23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="19.72"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="C2" s="0" t="s">
+        <v>157</v>
+      </c>
+      <c r="D2" s="0" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="0" t="str">
+        <f aca="false">+B2</f>
+        <v>-B2</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>159</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>147</v>
+      </c>
+      <c r="C4" s="0" t="s">
+        <v>160</v>
+      </c>
+      <c r="D4" s="0" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>148</v>
+      </c>
+      <c r="C5" s="0" t="s">
+        <v>161</v>
+      </c>
+      <c r="D5" s="0" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="C6" s="0" t="s">
+        <v>163</v>
+      </c>
+      <c r="D6" s="0" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="C7" s="0" t="s">
+        <v>165</v>
+      </c>
+      <c r="D7" s="0" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C18" s="5"/>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,obyčejné"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,obyčejné"&amp;12Stránka &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
@@ -1689,6 +2183,372 @@
       </c>
       <c r="D6" s="0" t="s">
         <v>34</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,obyčejné"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,obyčejné"&amp;12Stránka &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultColWidth="11.6875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="23.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="20.83"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" s="0" t="s">
+        <v>166</v>
+      </c>
+      <c r="D2" s="0" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>168</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>169</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="D4" s="0" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" s="0" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" s="0" t="s">
+        <v>167</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,obyčejné"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,obyčejné"&amp;12Stránka &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultColWidth="11.6875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="26.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="20.83"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" s="0" t="s">
+        <v>170</v>
+      </c>
+      <c r="D2" s="0" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>171</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>172</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>148</v>
+      </c>
+      <c r="C4" s="0" t="s">
+        <v>173</v>
+      </c>
+      <c r="D4" s="0" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>147</v>
+      </c>
+      <c r="C5" s="0" t="s">
+        <v>174</v>
+      </c>
+      <c r="D5" s="0" t="s">
+        <v>167</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,obyčejné"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,obyčejné"&amp;12Stránka &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultColWidth="11.6875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="26.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="20.83"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>95</v>
+      </c>
+      <c r="C2" s="0" t="s">
+        <v>175</v>
+      </c>
+      <c r="D2" s="0" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>175</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>95</v>
+      </c>
+      <c r="C4" s="0" t="s">
+        <v>175</v>
+      </c>
+      <c r="D4" s="0" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" s="0" t="s">
+        <v>176</v>
+      </c>
+      <c r="D5" s="0" t="s">
+        <v>167</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,obyčejné"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,obyčejné"&amp;12Stránka &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr defaultColWidth="11.6875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="26.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="20.83"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>177</v>
+      </c>
+      <c r="C2" s="0" t="s">
+        <v>178</v>
+      </c>
+      <c r="D2" s="0" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>177</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>178</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>167</v>
       </c>
     </row>
   </sheetData>

--- a/Manual/source/CZ/tab/connectors.xlsx
+++ b/Manual/source/CZ/tab/connectors.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="22"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="25"/>
   </bookViews>
   <sheets>
     <sheet name="rozcestnik" sheetId="1" state="visible" r:id="rId2"/>
@@ -31,6 +31,9 @@
     <sheet name="P7_BR_4pin_Microfit" sheetId="21" state="visible" r:id="rId22"/>
     <sheet name="P8_BR_4pin_Microfit" sheetId="22" state="visible" r:id="rId23"/>
     <sheet name="P3_Term_2pin_Microfit" sheetId="23" state="visible" r:id="rId24"/>
+    <sheet name="X4_M1_6pin_SLS" sheetId="24" state="visible" r:id="rId25"/>
+    <sheet name="X2_PWR_10pin_BLZP" sheetId="25" state="visible" r:id="rId26"/>
+    <sheet name="X2_320_DC_1778078" sheetId="26" state="visible" r:id="rId27"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -42,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="199">
   <si>
     <t xml:space="preserve">Toto je sešit se zdrojovými tabulkami popisu konektorů TGZ/TGS v češtině. Každý list odpovídá jednomu unikátnímu typu konektoru. Jelikož se často konektory v rámci TGZ opakují (typicky ty na řídicií desce), jsou zde jen jednou. Tj. Např. IO konektor 22pin weidmuller BCZ se používá pořád dokola, je zde tedy zanesen jen jednou jako „X8_IO_22pin_BCZ“</t>
   </si>
@@ -615,6 +618,66 @@
   </si>
   <si>
     <t xml:space="preserve">Teplotní čidlo PT1000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0,2 ~ 2,5 mm2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Střední pracovní vodič</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fáze </t>
+  </si>
+  <si>
+    <t xml:space="preserve">+RB </t>
+  </si>
+  <si>
+    <t xml:space="preserve">+ Brzdný odpor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-RB </t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Brzdný odpor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+DC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">+ Napájení meziobvodu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-DC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Napájení meziobvodu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">T+ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">+ Termistor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T- </t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Termistor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+140 ~ +320V</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max. 6 mm2</t>
   </si>
 </sst>
 </file>
@@ -724,16 +787,12 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
@@ -746,6 +805,10 @@
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -826,9 +889,9 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H17"/>
-  <sheetFormatPr defaultColWidth="12.23828125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.25390625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="13.8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="13.81"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="14.59"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="31.81"/>
   </cols>
@@ -975,7 +1038,7 @@
       <c r="G11" s="0" t="s">
         <v>16</v>
       </c>
-      <c r="H11" s="4" t="s">
+      <c r="H11" s="3" t="s">
         <v>17</v>
       </c>
     </row>
@@ -988,7 +1051,7 @@
       <c r="G12" s="0" t="s">
         <v>18</v>
       </c>
-      <c r="H12" s="4" t="s">
+      <c r="H12" s="3" t="s">
         <v>19</v>
       </c>
     </row>
@@ -1001,7 +1064,7 @@
       <c r="G13" s="0" t="s">
         <v>20</v>
       </c>
-      <c r="H13" s="4" t="s">
+      <c r="H13" s="3" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1014,7 +1077,7 @@
       <c r="G14" s="0" t="s">
         <v>22</v>
       </c>
-      <c r="H14" s="4" t="s">
+      <c r="H14" s="3" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1027,7 +1090,7 @@
       <c r="G15" s="0" t="s">
         <v>24</v>
       </c>
-      <c r="H15" s="4" t="s">
+      <c r="H15" s="3" t="s">
         <v>25</v>
       </c>
     </row>
@@ -1040,7 +1103,7 @@
       <c r="G16" s="0" t="s">
         <v>26</v>
       </c>
-      <c r="H16" s="4" t="s">
+      <c r="H16" s="3" t="s">
         <v>27</v>
       </c>
     </row>
@@ -1087,7 +1150,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D18"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="19.31"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="17.78"/>
@@ -1193,7 +1256,7 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C18" s="5"/>
+      <c r="C18" s="4"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -1212,7 +1275,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D18"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="19.31"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="17.78"/>
@@ -1318,7 +1381,7 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C18" s="5"/>
+      <c r="C18" s="4"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -1337,7 +1400,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultColWidth="11.6875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.70703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="18.38"/>
@@ -1445,7 +1508,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D18"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="19.31"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="17.78"/>
@@ -1495,7 +1558,7 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C18" s="5"/>
+      <c r="C18" s="4"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -1514,7 +1577,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D18"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="19.31"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="17.78"/>
@@ -1578,7 +1641,7 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C18" s="5"/>
+      <c r="C18" s="4"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -1597,7 +1660,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultColWidth="11.6875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.70703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="18.38"/>
@@ -1691,7 +1754,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D18"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="19.31"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="17.78"/>
@@ -1755,7 +1818,7 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C18" s="5"/>
+      <c r="C18" s="4"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -1774,7 +1837,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D18"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="19.31"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="17.78"/>
@@ -1852,7 +1915,7 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C18" s="5"/>
+      <c r="C18" s="4"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -1871,7 +1934,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D18"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="19.31"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="17.78"/>
@@ -1949,7 +2012,7 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C18" s="5"/>
+      <c r="C18" s="4"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -1968,7 +2031,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D18"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="19.31"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="27.23"/>
@@ -1993,7 +2056,7 @@
       <c r="A2" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="5" t="s">
         <v>156</v>
       </c>
       <c r="C2" s="0" t="s">
@@ -2050,7 +2113,7 @@
       <c r="A6" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="5" t="s">
         <v>162</v>
       </c>
       <c r="C6" s="0" t="s">
@@ -2064,7 +2127,7 @@
       <c r="A7" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="5" t="s">
         <v>164</v>
       </c>
       <c r="C7" s="0" t="s">
@@ -2075,7 +2138,7 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C18" s="5"/>
+      <c r="C18" s="4"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -2094,7 +2157,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultColWidth="11.6875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.70703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="18.38"/>
@@ -2202,11 +2265,11 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultColWidth="11.6875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.70703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18.38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="23.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="23.35"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="20.83"/>
   </cols>
   <sheetData>
@@ -2311,7 +2374,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultColWidth="11.6875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.70703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18.38"/>
@@ -2406,7 +2469,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultColWidth="11.6875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.70703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18.38"/>
@@ -2501,7 +2564,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultColWidth="11.6875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.70703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18.38"/>
@@ -2549,6 +2612,390 @@
       </c>
       <c r="D3" s="0" t="s">
         <v>167</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,obyčejné"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,obyčejné"&amp;12Stránka &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D18"/>
+  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="19.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="17.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="19.72"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>126</v>
+      </c>
+      <c r="C2" s="0" t="s">
+        <v>127</v>
+      </c>
+      <c r="D2" s="0" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>129</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>130</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>131</v>
+      </c>
+      <c r="C4" s="0" t="s">
+        <v>132</v>
+      </c>
+      <c r="D4" s="0" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>133</v>
+      </c>
+      <c r="C5" s="0" t="s">
+        <v>134</v>
+      </c>
+      <c r="D5" s="0" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="C6" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="D6" s="0" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>137</v>
+      </c>
+      <c r="C7" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="D7" s="0" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C18" s="4"/>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,obyčejné"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,obyčejné"&amp;12Stránka &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D18"/>
+  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="19.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="19.72"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C18" s="4"/>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,obyčejné"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,obyčejné"&amp;12Stránka &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13.1"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2" s="0" t="s">
+        <v>197</v>
+      </c>
+      <c r="D2" s="0" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>47</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>131</v>
+      </c>
+      <c r="C4" s="0" t="s">
+        <v>132</v>
+      </c>
+      <c r="D4" s="0" t="s">
+        <v>198</v>
       </c>
     </row>
   </sheetData>
@@ -2568,7 +3015,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
@@ -2629,7 +3076,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D23"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="30.7"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="19.72"/>
@@ -2974,7 +3421,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="17.09"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="18.33"/>
@@ -3067,7 +3514,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14.62"/>
   </cols>
@@ -3113,7 +3560,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D18"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="19.31"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="17.78"/>
@@ -3303,7 +3750,7 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C18" s="5"/>
+      <c r="C18" s="4"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -3322,7 +3769,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D18"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="19.31"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="17.78"/>
@@ -3456,7 +3903,7 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C18" s="5"/>
+      <c r="C18" s="4"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -3475,7 +3922,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D18"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="19.31"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="17.78"/>
@@ -3609,7 +4056,7 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C18" s="5"/>
+      <c r="C18" s="4"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/Manual/source/CZ/tab/connectors.xlsx
+++ b/Manual/source/CZ/tab/connectors.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="25"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="27"/>
   </bookViews>
   <sheets>
     <sheet name="rozcestnik" sheetId="1" state="visible" r:id="rId2"/>
@@ -34,6 +34,8 @@
     <sheet name="X4_M1_6pin_SLS" sheetId="24" state="visible" r:id="rId25"/>
     <sheet name="X2_PWR_10pin_BLZP" sheetId="25" state="visible" r:id="rId26"/>
     <sheet name="X2_320_DC_1778078" sheetId="26" state="visible" r:id="rId27"/>
+    <sheet name="X4_M1_6pin_BLF" sheetId="27" state="visible" r:id="rId28"/>
+    <sheet name="X2_PWR_12pin_BLZ" sheetId="28" state="visible" r:id="rId29"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -45,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="607" uniqueCount="214">
   <si>
     <t xml:space="preserve">Toto je sešit se zdrojovými tabulkami popisu konektorů TGZ/TGS v češtině. Každý list odpovídá jednomu unikátnímu typu konektoru. Jelikož se často konektory v rámci TGZ opakují (typicky ty na řídicií desce), jsou zde jen jednou. Tj. Např. IO konektor 22pin weidmuller BCZ se používá pořád dokola, je zde tedy zanesen jen jednou jako „X8_IO_22pin_BCZ“</t>
   </si>
@@ -678,6 +680,51 @@
   </si>
   <si>
     <t xml:space="preserve">Max. 6 mm2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0,5 ~ 2,5 mm2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L1 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fáze 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L2 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fáze 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L3 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fáze 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RBin </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brzdný odpor interní</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SEL </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Volba brzdného odporu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RBex </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brzdný odpor externí</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+Termistor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-Termistor</t>
   </si>
 </sst>
 </file>
@@ -889,9 +936,9 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H17"/>
-  <sheetFormatPr defaultColWidth="12.25390625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="12.2734375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="13.81"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="13.82"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="14.59"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="31.81"/>
   </cols>
@@ -1150,7 +1197,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D18"/>
-  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="19.31"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="17.78"/>
@@ -1275,7 +1322,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D18"/>
-  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="19.31"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="17.78"/>
@@ -1400,7 +1447,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultColWidth="11.70703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="18.38"/>
@@ -1508,7 +1555,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D18"/>
-  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="19.31"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="17.78"/>
@@ -1577,7 +1624,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D18"/>
-  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="19.31"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="17.78"/>
@@ -1660,7 +1707,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultColWidth="11.70703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="18.38"/>
@@ -1754,7 +1801,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D18"/>
-  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="19.31"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="17.78"/>
@@ -1837,7 +1884,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D18"/>
-  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="19.31"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="17.78"/>
@@ -1934,7 +1981,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D18"/>
-  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="19.31"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="17.78"/>
@@ -2031,7 +2078,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D18"/>
-  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="19.31"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="27.23"/>
@@ -2157,7 +2204,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultColWidth="11.70703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="18.38"/>
@@ -2265,7 +2312,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultColWidth="11.70703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18.38"/>
@@ -2374,7 +2421,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultColWidth="11.70703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18.38"/>
@@ -2469,7 +2516,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultColWidth="11.70703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18.38"/>
@@ -2564,7 +2611,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultColWidth="11.70703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6.29"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18.38"/>
@@ -2631,7 +2678,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D18"/>
-  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="19.31"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="17.78"/>
@@ -2756,7 +2803,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D18"/>
-  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="19.31"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22.79"/>
@@ -2937,7 +2984,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13.1"/>
   </cols>
@@ -2996,6 +3043,337 @@
       </c>
       <c r="D4" s="0" t="s">
         <v>198</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,obyčejné"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,obyčejné"&amp;12Stránka &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D18"/>
+  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="19.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="17.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="19.72"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>126</v>
+      </c>
+      <c r="C2" s="0" t="s">
+        <v>127</v>
+      </c>
+      <c r="D2" s="0" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>129</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>130</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>131</v>
+      </c>
+      <c r="C4" s="0" t="s">
+        <v>132</v>
+      </c>
+      <c r="D4" s="0" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>133</v>
+      </c>
+      <c r="C5" s="0" t="s">
+        <v>134</v>
+      </c>
+      <c r="D5" s="0" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>135</v>
+      </c>
+      <c r="C6" s="0" t="s">
+        <v>136</v>
+      </c>
+      <c r="D6" s="0" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>137</v>
+      </c>
+      <c r="C7" s="0" t="s">
+        <v>138</v>
+      </c>
+      <c r="D7" s="0" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C18" s="4"/>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,obyčejné"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,obyčejné"&amp;12Stránka &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D13"/>
+  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="19.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="19.72"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>131</v>
+      </c>
+      <c r="C2" s="0" t="s">
+        <v>132</v>
+      </c>
+      <c r="D2" s="0" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>200</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>201</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>202</v>
+      </c>
+      <c r="C4" s="0" t="s">
+        <v>203</v>
+      </c>
+      <c r="D4" s="0" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>204</v>
+      </c>
+      <c r="C5" s="0" t="s">
+        <v>205</v>
+      </c>
+      <c r="D5" s="0" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>206</v>
+      </c>
+      <c r="C6" s="0" t="s">
+        <v>207</v>
+      </c>
+      <c r="D6" s="0" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>208</v>
+      </c>
+      <c r="C7" s="0" t="s">
+        <v>209</v>
+      </c>
+      <c r="D7" s="0" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>210</v>
+      </c>
+      <c r="C8" s="0" t="s">
+        <v>211</v>
+      </c>
+      <c r="D8" s="0" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="0" t="s">
+        <v>188</v>
+      </c>
+      <c r="C9" s="0" t="s">
+        <v>189</v>
+      </c>
+      <c r="D9" s="0" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="0" t="s">
+        <v>190</v>
+      </c>
+      <c r="C10" s="0" t="s">
+        <v>191</v>
+      </c>
+      <c r="D10" s="0" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="0" t="s">
+        <v>192</v>
+      </c>
+      <c r="C11" s="0" t="s">
+        <v>132</v>
+      </c>
+      <c r="D11" s="0" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="0" t="s">
+        <v>193</v>
+      </c>
+      <c r="C12" s="0" t="s">
+        <v>212</v>
+      </c>
+      <c r="D12" s="0" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="0" t="s">
+        <v>195</v>
+      </c>
+      <c r="C13" s="0" t="s">
+        <v>213</v>
+      </c>
+      <c r="D13" s="0" t="s">
+        <v>128</v>
       </c>
     </row>
   </sheetData>
@@ -3015,7 +3393,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
@@ -3076,7 +3454,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D23"/>
-  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="30.7"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="19.72"/>
@@ -3421,7 +3799,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="17.09"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="18.33"/>
@@ -3514,7 +3892,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14.62"/>
   </cols>
@@ -3560,7 +3938,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D18"/>
-  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="19.31"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="17.78"/>
@@ -3769,7 +4147,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D18"/>
-  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="19.31"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="17.78"/>
@@ -3922,7 +4300,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D18"/>
-  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="19.31"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="17.78"/>

--- a/Manual/source/CZ/tab/connectors.xlsx
+++ b/Manual/source/CZ/tab/connectors.xlsx
@@ -5,37 +5,39 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="27"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="29"/>
   </bookViews>
   <sheets>
-    <sheet name="rozcestnik" sheetId="1" state="visible" r:id="rId2"/>
-    <sheet name="X1_24V_5pin_BCZ" sheetId="2" state="visible" r:id="rId3"/>
-    <sheet name="X2_48_DC_1778065" sheetId="3" state="visible" r:id="rId4"/>
-    <sheet name="X8_IO_22pin_BCZ" sheetId="4" state="visible" r:id="rId5"/>
-    <sheet name="X10_CAN_4pin_BCZ" sheetId="5" state="visible" r:id="rId6"/>
-    <sheet name="LEDsigAx12" sheetId="6" state="visible" r:id="rId7"/>
-    <sheet name="X5_FBE_12pin_BCZ" sheetId="7" state="visible" r:id="rId8"/>
-    <sheet name="X6_FB1_8pin_BCZ" sheetId="8" state="visible" r:id="rId9"/>
-    <sheet name="X7_FB2_8pin_BCZ" sheetId="9" state="visible" r:id="rId10"/>
-    <sheet name="X3_M1_6pin_BLZP" sheetId="10" state="visible" r:id="rId11"/>
-    <sheet name="X4_M2_6pin_BLZP" sheetId="11" state="visible" r:id="rId12"/>
-    <sheet name="X1_24V_5pin_Microlock" sheetId="12" state="visible" r:id="rId13"/>
-    <sheet name="X3_DCbus_2pin_pressfit" sheetId="13" state="visible" r:id="rId14"/>
-    <sheet name="X3_M1_3pin_pressfit" sheetId="14" state="visible" r:id="rId15"/>
-    <sheet name="X4_BR_4pin_Microlock" sheetId="15" state="visible" r:id="rId16"/>
-    <sheet name="X2_DCbus_3pin_wago_2636" sheetId="16" state="visible" r:id="rId17"/>
-    <sheet name="X3_M1_4pin_wago_2626" sheetId="17" state="visible" r:id="rId18"/>
-    <sheet name="X4_M2_4pin_wago_2626" sheetId="18" state="visible" r:id="rId19"/>
-    <sheet name="XBR_BR_6pin_BLF" sheetId="19" state="visible" r:id="rId20"/>
-    <sheet name="X1_24V_5pin_Microfit" sheetId="20" state="visible" r:id="rId21"/>
-    <sheet name="P7_BR_4pin_Microfit" sheetId="21" state="visible" r:id="rId22"/>
-    <sheet name="P8_BR_4pin_Microfit" sheetId="22" state="visible" r:id="rId23"/>
-    <sheet name="P3_Term_2pin_Microfit" sheetId="23" state="visible" r:id="rId24"/>
-    <sheet name="X4_M1_6pin_SLS" sheetId="24" state="visible" r:id="rId25"/>
-    <sheet name="X2_PWR_10pin_BLZP" sheetId="25" state="visible" r:id="rId26"/>
-    <sheet name="X2_320_DC_1778078" sheetId="26" state="visible" r:id="rId27"/>
-    <sheet name="X4_M1_6pin_BLF" sheetId="27" state="visible" r:id="rId28"/>
-    <sheet name="X2_PWR_12pin_BLZ" sheetId="28" state="visible" r:id="rId29"/>
+    <sheet name="rozcestnik" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="X1_24V_5pin_BCZ" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="X2_48_DC_1778065" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="X8_IO_22pin_BCZ" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="X10_CAN_4pin_BCZ" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="LEDsigAx12" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="X5_FBE_12pin_BCZ" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="X6_FB1_8pin_BCZ" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="X7_FB2_8pin_BCZ" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="X3_M1_6pin_BLZP" sheetId="10" state="visible" r:id="rId12"/>
+    <sheet name="X4_M2_6pin_BLZP" sheetId="11" state="visible" r:id="rId13"/>
+    <sheet name="X1_24V_5pin_Microlock" sheetId="12" state="visible" r:id="rId14"/>
+    <sheet name="X3_DCbus_2pin_pressfit" sheetId="13" state="visible" r:id="rId15"/>
+    <sheet name="X3_M1_3pin_pressfit" sheetId="14" state="visible" r:id="rId16"/>
+    <sheet name="X4_BR_4pin_Microlock" sheetId="15" state="visible" r:id="rId17"/>
+    <sheet name="X2_DCbus_3pin_wago_2636" sheetId="16" state="visible" r:id="rId18"/>
+    <sheet name="X3_M1_4pin_wago_2626" sheetId="17" state="visible" r:id="rId19"/>
+    <sheet name="X4_M2_4pin_wago_2626" sheetId="18" state="visible" r:id="rId20"/>
+    <sheet name="XBR_BR_6pin_BLF" sheetId="19" state="visible" r:id="rId21"/>
+    <sheet name="X1_24V_5pin_Microfit" sheetId="20" state="visible" r:id="rId22"/>
+    <sheet name="P7_BR_4pin_Microfit" sheetId="21" state="visible" r:id="rId23"/>
+    <sheet name="P8_BR_4pin_Microfit" sheetId="22" state="visible" r:id="rId24"/>
+    <sheet name="P3_Term_2pin_Microfit" sheetId="23" state="visible" r:id="rId25"/>
+    <sheet name="X4_M1_6pin_SLS" sheetId="24" state="visible" r:id="rId26"/>
+    <sheet name="X2_PWR_10pin_BLZP" sheetId="25" state="visible" r:id="rId27"/>
+    <sheet name="X2_320_DC_1778078" sheetId="26" state="visible" r:id="rId28"/>
+    <sheet name="X4_M1_6pin_BLF" sheetId="27" state="visible" r:id="rId29"/>
+    <sheet name="X2_PWR_12pin_BLZ" sheetId="28" state="visible" r:id="rId30"/>
+    <sheet name="X2_D560DCbus" sheetId="29" state="visible" r:id="rId31"/>
+    <sheet name="X3_M1_4pin_wago_2636" sheetId="30" state="visible" r:id="rId32"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -47,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="607" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="219">
   <si>
     <t xml:space="preserve">Toto je sešit se zdrojovými tabulkami popisu konektorů TGZ/TGS v češtině. Každý list odpovídá jednomu unikátnímu typu konektoru. Jelikož se často konektory v rámci TGZ opakují (typicky ty na řídicií desce), jsou zde jen jednou. Tj. Např. IO konektor 22pin weidmuller BCZ se používá pořád dokola, je zde tedy zanesen jen jednou jako „X8_IO_22pin_BCZ“</t>
   </si>
@@ -725,6 +727,21 @@
   </si>
   <si>
     <t xml:space="preserve">-Termistor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-DC IN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+ DC bus vstup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dle oka</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+DC IN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- DC bus vstup</t>
   </si>
 </sst>
 </file>
@@ -829,32 +846,36 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -930,238 +951,344 @@
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="LibreOffice">
+      <a:dk1>
+        <a:srgbClr val="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:srgbClr val="ffffff"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="000000"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="ffffff"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="18a303"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="0369a3"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="a33e03"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8e03a3"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="c99c00"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="c9211e"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000ee"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="551a8b"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme>
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H17"/>
   <sheetFormatPr defaultColWidth="12.2734375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="13.82"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="14.59"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="31.81"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="13.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="14.59"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="31.81"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="0" t="s">
+      <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="0" t="s">
+      <c r="D8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E8" s="0" t="s">
+      <c r="E8" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F8" s="0" t="s">
+      <c r="F8" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G8" s="0" t="s">
+      <c r="G8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H8" s="0" t="s">
+      <c r="H8" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="0" t="s">
+      <c r="C9" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="0" t="n">
+      <c r="D9" s="1" t="n">
         <v>48</v>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="E9" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="F9" s="2" t="n">
+      <c r="F9" s="3" t="n">
         <v>100</v>
       </c>
-      <c r="G9" s="0" t="s">
+      <c r="G9" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H9" s="3" t="s">
+      <c r="H9" s="4" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C10" s="0" t="s">
+      <c r="C10" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="0" t="n">
+      <c r="D10" s="1" t="n">
         <v>48</v>
       </c>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="0" t="s">
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H10" s="3" t="s">
+      <c r="H10" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C11" s="0" t="s">
+      <c r="C11" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="0" t="n">
+      <c r="D11" s="1" t="n">
         <v>48</v>
       </c>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="0" t="s">
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H11" s="3" t="s">
+      <c r="H11" s="4" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D12" s="0" t="n">
+      <c r="D12" s="1" t="n">
         <v>48</v>
       </c>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="0" t="s">
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="H12" s="3" t="s">
+      <c r="H12" s="4" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D13" s="0" t="n">
+      <c r="D13" s="1" t="n">
         <v>48</v>
       </c>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="0" t="s">
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H13" s="3" t="s">
+      <c r="H13" s="4" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D14" s="0" t="n">
+      <c r="D14" s="1" t="n">
         <v>48</v>
       </c>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="0" t="s">
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="H14" s="3" t="s">
+      <c r="H14" s="4" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D15" s="0" t="n">
+      <c r="D15" s="1" t="n">
         <v>48</v>
       </c>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="0" t="s">
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H15" s="3" t="s">
+      <c r="H15" s="4" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D16" s="0" t="n">
+      <c r="D16" s="1" t="n">
         <v>48</v>
       </c>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="0" t="s">
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H16" s="3" t="s">
+      <c r="H16" s="4" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D17" s="0" t="n">
+      <c r="D17" s="1" t="n">
         <v>48</v>
       </c>
-      <c r="E17" s="0" t="n">
+      <c r="E17" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="F17" s="0" t="n">
+      <c r="F17" s="1" t="n">
         <v>250</v>
       </c>
     </row>
@@ -1192,118 +1319,118 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D18"/>
   <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="19.31"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="17.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="19.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="19.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="17.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="19.72"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+      <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="1" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+      <c r="A5" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" s="1" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
+      <c r="A6" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" s="1" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
+      <c r="A7" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="D7" s="0" t="s">
+      <c r="D7" s="1" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C18" s="4"/>
+      <c r="C18" s="5"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -1317,118 +1444,118 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D18"/>
   <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="19.31"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="17.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="19.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="19.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="17.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="19.72"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+      <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="1" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+      <c r="A5" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" s="1" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
+      <c r="A6" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" s="1" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
+      <c r="A7" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="D7" s="0" t="s">
+      <c r="D7" s="1" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C18" s="4"/>
+      <c r="C18" s="5"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -1442,99 +1569,99 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D6"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="18.38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="18.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="12.83"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+      <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="1" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+      <c r="A5" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" s="1" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
+      <c r="A6" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" s="1" t="s">
         <v>139</v>
       </c>
     </row>
@@ -1550,62 +1677,62 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D18"/>
   <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="19.31"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="17.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="19.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="19.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="17.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="19.72"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+      <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C18" s="4"/>
+      <c r="C18" s="5"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -1619,76 +1746,76 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D18"/>
   <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="19.31"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="17.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="19.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="19.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="17.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="19.72"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+      <c r="A2" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="1" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C18" s="4"/>
+      <c r="C18" s="5"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -1702,85 +1829,85 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D5"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="18.38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="18.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="12.83"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+      <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="1" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+      <c r="A5" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" s="1" t="s">
         <v>139</v>
       </c>
     </row>
@@ -1796,76 +1923,76 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D18"/>
   <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="19.31"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="17.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="19.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="19.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="17.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="19.72"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+      <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="1" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C18" s="4"/>
+      <c r="C18" s="5"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -1879,90 +2006,90 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D18"/>
   <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="19.31"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="17.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="19.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="19.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="17.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="19.72"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+      <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="1" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+      <c r="A5" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" s="1" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C18" s="4"/>
+      <c r="C18" s="5"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -1976,90 +2103,90 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D18"/>
   <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="19.31"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="17.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="19.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="19.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="17.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="19.72"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+      <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="1" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+      <c r="A5" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" s="1" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C18" s="4"/>
+      <c r="C18" s="5"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -2073,119 +2200,119 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D18"/>
   <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="19.31"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="27.23"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="19.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="19.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="27.23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="19.72"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+      <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="0" t="str">
+      <c r="B3" s="1" t="str">
         <f aca="false">+B2</f>
         <v>-B2</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="1" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+      <c r="A5" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" s="1" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
+      <c r="A6" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" s="1" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
+      <c r="A7" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="D7" s="0" t="s">
+      <c r="D7" s="1" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C18" s="4"/>
+      <c r="C18" s="5"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -2199,99 +2326,99 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D6"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="18.38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="18.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="12.83"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+      <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="1" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+      <c r="A5" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" s="1" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
+      <c r="A6" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" s="1" t="s">
         <v>34</v>
       </c>
     </row>
@@ -2307,100 +2434,100 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D6"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18.38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="23.35"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="20.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="23.35"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="20.83"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+      <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="1" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+      <c r="A5" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" s="1" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
+      <c r="A6" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" s="1" t="s">
         <v>167</v>
       </c>
     </row>
@@ -2416,86 +2543,86 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D5"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18.38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="26.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="20.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="26.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="20.83"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+      <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="1" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+      <c r="A5" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" s="1" t="s">
         <v>167</v>
       </c>
     </row>
@@ -2511,86 +2638,86 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D5"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18.38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="26.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="20.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="26.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="20.83"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+      <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="1" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+      <c r="A5" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" s="1" t="s">
         <v>167</v>
       </c>
     </row>
@@ -2606,58 +2733,58 @@
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D3"/>
   <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18.38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="26.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="20.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="26.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="20.83"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+      <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>167</v>
       </c>
     </row>
@@ -2673,118 +2800,118 @@
 </file>
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D18"/>
   <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="19.31"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="17.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="19.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="19.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="17.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="19.72"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+      <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="1" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+      <c r="A5" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" s="1" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
+      <c r="A6" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" s="1" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
+      <c r="A7" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="D7" s="0" t="s">
+      <c r="D7" s="1" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C18" s="4"/>
+      <c r="C18" s="5"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -2798,174 +2925,174 @@
 </file>
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D18"/>
   <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="19.31"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22.79"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="19.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="19.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="22.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="19.72"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="7" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="6" t="n">
+      <c r="A2" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="7" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="n">
+      <c r="A3" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="7" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="n">
+      <c r="A4" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="7" t="s">
         <v>183</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="7" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="n">
+      <c r="A5" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="7" t="s">
         <v>184</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="7" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="n">
+      <c r="A6" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="7" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="n">
+      <c r="A7" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="7" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="n">
+      <c r="A8" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="7" t="s">
         <v>190</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="7" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="n">
+      <c r="A9" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="7" t="s">
         <v>192</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="7" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6" t="n">
+      <c r="A10" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="7" t="s">
         <v>193</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="7" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6" t="n">
+      <c r="A11" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="7" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C18" s="4"/>
+      <c r="C18" s="5"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -2979,69 +3106,69 @@
 </file>
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D4"/>
   <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="13.1"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+      <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="1" t="s">
         <v>198</v>
       </c>
     </row>
@@ -3057,118 +3184,118 @@
 </file>
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D18"/>
   <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="19.31"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="17.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="19.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="19.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="17.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="19.72"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+      <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="1" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+      <c r="A5" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" s="1" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
+      <c r="A6" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" s="1" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
+      <c r="A7" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="D7" s="0" t="s">
+      <c r="D7" s="1" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C18" s="4"/>
+      <c r="C18" s="5"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -3182,199 +3309,295 @@
 </file>
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D13"/>
   <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="19.31"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22.79"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="19.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="19.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="22.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="19.72"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+      <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="1" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+      <c r="A5" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" s="1" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
+      <c r="A6" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" s="1" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
+      <c r="A7" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="D7" s="0" t="s">
+      <c r="D7" s="1" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="n">
+      <c r="A8" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C8" s="0" t="s">
+      <c r="C8" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="D8" s="0" t="s">
+      <c r="D8" s="1" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="n">
+      <c r="A9" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="C9" s="0" t="s">
+      <c r="C9" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="D9" s="0" t="s">
+      <c r="D9" s="1" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="n">
+      <c r="A10" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="C10" s="0" t="s">
+      <c r="C10" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="D10" s="0" t="s">
+      <c r="D10" s="1" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="n">
+      <c r="A11" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="C11" s="0" t="s">
+      <c r="C11" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="D11" s="0" t="s">
+      <c r="D11" s="1" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="n">
+      <c r="A12" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="C12" s="0" t="s">
+      <c r="C12" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="D12" s="0" t="s">
+      <c r="D12" s="1" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="n">
+      <c r="A13" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="0" t="s">
+      <c r="B13" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="C13" s="0" t="s">
+      <c r="C13" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="D13" s="0" t="s">
+      <c r="D13" s="1" t="s">
         <v>128</v>
       </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,obyčejné"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,obyčejné"&amp;12Stránka &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D13"/>
+  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="19.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="22.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="19.72"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1"/>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1"/>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1"/>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1"/>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1"/>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1"/>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1"/>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -3388,7 +3611,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
@@ -3396,46 +3619,143 @@
   <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+      <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>45</v>
       </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,obyčejné"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,obyčejné"&amp;12Stránka &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D18"/>
+  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="19.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="17.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="19.72"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C18" s="5"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -3449,336 +3769,336 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D23"/>
   <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="30.7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="19.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="30.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="19.72"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+      <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="1" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+      <c r="A5" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" s="1" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
+      <c r="A6" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" s="1" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
+      <c r="A7" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D7" s="0" t="s">
+      <c r="D7" s="1" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="n">
+      <c r="A8" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C8" s="0" t="s">
+      <c r="C8" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="D8" s="0" t="s">
+      <c r="D8" s="1" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="n">
+      <c r="A9" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C9" s="0" t="s">
+      <c r="C9" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="D9" s="0" t="s">
+      <c r="D9" s="1" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="n">
+      <c r="A10" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="C10" s="0" t="s">
+      <c r="C10" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D10" s="0" t="s">
+      <c r="D10" s="1" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="n">
+      <c r="A11" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C11" s="0" t="s">
+      <c r="C11" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="D11" s="0" t="s">
+      <c r="D11" s="1" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="n">
+      <c r="A12" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C12" s="0" t="s">
+      <c r="C12" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D12" s="0" t="s">
+      <c r="D12" s="1" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="n">
+      <c r="A13" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="0" t="s">
+      <c r="B13" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C13" s="0" t="s">
+      <c r="C13" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D13" s="0" t="s">
+      <c r="D13" s="1" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="n">
+      <c r="A14" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="0" t="s">
+      <c r="B14" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C14" s="0" t="s">
+      <c r="C14" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D14" s="0" t="s">
+      <c r="D14" s="1" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="n">
+      <c r="A15" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="0" t="s">
+      <c r="B15" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C15" s="0" t="s">
+      <c r="C15" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D15" s="0" t="s">
+      <c r="D15" s="1" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="n">
+      <c r="A16" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="0" t="s">
+      <c r="B16" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C16" s="0" t="s">
+      <c r="C16" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="D16" s="0" t="s">
+      <c r="D16" s="1" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="n">
+      <c r="A17" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="0" t="s">
+      <c r="B17" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="C17" s="0" t="s">
+      <c r="C17" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="D17" s="0" t="s">
+      <c r="D17" s="1" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="n">
+      <c r="A18" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="0" t="s">
+      <c r="B18" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="C18" s="0" t="s">
+      <c r="C18" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D18" s="0" t="s">
+      <c r="D18" s="1" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="n">
+      <c r="A19" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="0" t="s">
+      <c r="B19" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="C19" s="0" t="s">
+      <c r="C19" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D19" s="0" t="s">
+      <c r="D19" s="1" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="n">
+      <c r="A20" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="0" t="s">
+      <c r="B20" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C20" s="0" t="s">
+      <c r="C20" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="D20" s="0" t="s">
+      <c r="D20" s="1" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="n">
+      <c r="A21" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="0" t="s">
+      <c r="B21" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C21" s="0" t="s">
+      <c r="C21" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="D21" s="0" t="s">
+      <c r="D21" s="1" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="n">
+      <c r="A22" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="0" t="s">
+      <c r="B22" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="C22" s="0" t="s">
+      <c r="C22" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="D22" s="0" t="s">
+      <c r="D22" s="1" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="n">
+      <c r="A23" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="0" t="s">
+      <c r="B23" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="C23" s="0" t="s">
+      <c r="C23" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="D23" s="0" t="s">
+      <c r="D23" s="1" t="s">
         <v>50</v>
       </c>
     </row>
@@ -3794,84 +4114,84 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D5"/>
   <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="17.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="18.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="17.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="18.34"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+      <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="1" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+      <c r="A5" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" s="1" t="s">
         <v>50</v>
       </c>
     </row>
@@ -3887,37 +4207,37 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B3"/>
   <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14.62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.62"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>102</v>
       </c>
     </row>
@@ -3933,202 +4253,202 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D18"/>
   <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="19.31"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="17.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="19.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="19.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="17.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="19.72"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+      <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="1" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+      <c r="A5" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" s="1" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
+      <c r="A6" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" s="1" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
+      <c r="A7" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D7" s="0" t="s">
+      <c r="D7" s="1" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="n">
+      <c r="A8" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="C8" s="0" t="s">
+      <c r="C8" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="D8" s="0" t="s">
+      <c r="D8" s="1" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="n">
+      <c r="A9" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="C9" s="0" t="s">
+      <c r="C9" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D9" s="0" t="s">
+      <c r="D9" s="1" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="n">
+      <c r="A10" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="C10" s="0" t="s">
+      <c r="C10" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="D10" s="0" t="s">
+      <c r="D10" s="1" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="n">
+      <c r="A11" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="C11" s="0" t="s">
+      <c r="C11" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="D11" s="0" t="s">
+      <c r="D11" s="1" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="n">
+      <c r="A12" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C12" s="0" t="s">
+      <c r="C12" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="D12" s="0" t="s">
+      <c r="D12" s="1" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="n">
+      <c r="A13" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="0" t="s">
+      <c r="B13" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="C13" s="0" t="s">
+      <c r="C13" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="D13" s="0" t="s">
+      <c r="D13" s="1" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C18" s="4"/>
+      <c r="C18" s="5"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -4142,146 +4462,146 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D18"/>
   <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="19.31"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="17.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="19.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="19.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="17.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="19.72"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+      <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="1" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+      <c r="A5" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" s="1" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
+      <c r="A6" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" s="1" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
+      <c r="A7" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="D7" s="0" t="s">
+      <c r="D7" s="1" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="n">
+      <c r="A8" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C8" s="0" t="s">
+      <c r="C8" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="D8" s="0" t="s">
+      <c r="D8" s="1" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="n">
+      <c r="A9" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="C9" s="0" t="s">
+      <c r="C9" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="D9" s="0" t="s">
+      <c r="D9" s="1" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C18" s="4"/>
+      <c r="C18" s="5"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -4295,146 +4615,146 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D18"/>
   <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="19.31"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="17.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="19.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="19.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="17.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="19.72"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+      <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="1" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+      <c r="A5" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" s="1" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
+      <c r="A6" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" s="1" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
+      <c r="A7" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="D7" s="0" t="s">
+      <c r="D7" s="1" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="n">
+      <c r="A8" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C8" s="0" t="s">
+      <c r="C8" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="D8" s="0" t="s">
+      <c r="D8" s="1" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="n">
+      <c r="A9" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="C9" s="0" t="s">
+      <c r="C9" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="D9" s="0" t="s">
+      <c r="D9" s="1" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C18" s="4"/>
+      <c r="C18" s="5"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/Manual/source/CZ/tab/connectors.xlsx
+++ b/Manual/source/CZ/tab/connectors.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="29"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="35"/>
   </bookViews>
   <sheets>
     <sheet name="rozcestnik" sheetId="1" state="visible" r:id="rId3"/>
@@ -38,6 +38,12 @@
     <sheet name="X2_PWR_12pin_BLZ" sheetId="28" state="visible" r:id="rId30"/>
     <sheet name="X2_D560DCbus" sheetId="29" state="visible" r:id="rId31"/>
     <sheet name="X3_M1_4pin_wago_2636" sheetId="30" state="visible" r:id="rId32"/>
+    <sheet name="X4_M2_4pin_wago_2636" sheetId="31" state="visible" r:id="rId33"/>
+    <sheet name="X14_BR1_4pin_LSF" sheetId="32" state="visible" r:id="rId34"/>
+    <sheet name="X15_BR2_4pin_LSF" sheetId="33" state="visible" r:id="rId35"/>
+    <sheet name="X1_ACIN_PC5" sheetId="34" state="visible" r:id="rId36"/>
+    <sheet name="X2_DC_8pin_PC5" sheetId="35" state="visible" r:id="rId37"/>
+    <sheet name="X3_DO_4pin_BCZ" sheetId="36" state="visible" r:id="rId38"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -49,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="738" uniqueCount="243">
   <si>
     <t xml:space="preserve">Toto je sešit se zdrojovými tabulkami popisu konektorů TGZ/TGS v češtině. Každý list odpovídá jednomu unikátnímu typu konektoru. Jelikož se často konektory v rámci TGZ opakují (typicky ty na řídicií desce), jsou zde jen jednou. Tj. Např. IO konektor 22pin weidmuller BCZ se používá pořád dokola, je zde tedy zanesen jen jednou jako „X8_IO_22pin_BCZ“</t>
   </si>
@@ -723,9 +729,15 @@
     <t xml:space="preserve">Brzdný odpor externí</t>
   </si>
   <si>
+    <t xml:space="preserve">T+</t>
+  </si>
+  <si>
     <t xml:space="preserve">+Termistor</t>
   </si>
   <si>
+    <t xml:space="preserve">T-</t>
+  </si>
+  <si>
     <t xml:space="preserve">-Termistor</t>
   </si>
   <si>
@@ -742,6 +754,72 @@
   </si>
   <si>
     <t xml:space="preserve">- DC bus vstup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Brzda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0,13 ~ 1,5 mm2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+ Brzda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-T</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+T</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fáze</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  + DC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  - DC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  PE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  SEL </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  + RB </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  - RB </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  + T </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  - T </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RDY1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Signál „Ready“ kontakt 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RDY2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Signál „Ready“ kontakt 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ERR1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Signál „Error“ kontakt 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ERR2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Signál „Error“ kontakt 2</t>
   </si>
 </sst>
 </file>
@@ -3480,10 +3558,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>193</v>
+        <v>212</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>128</v>
@@ -3494,10 +3572,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>195</v>
+        <v>214</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>128</v>
@@ -3546,13 +3624,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3560,13 +3638,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>218</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3703,10 +3781,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>154</v>
@@ -3717,10 +3795,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>154</v>
@@ -3731,10 +3809,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>154</v>
@@ -3745,17 +3823,785 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>154</v>
       </c>
     </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="0"/>
+      <c r="C14" s="0"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="0"/>
+      <c r="C15" s="0"/>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="0"/>
+      <c r="C16" s="0"/>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="0"/>
+      <c r="C17" s="0"/>
+    </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C18" s="5"/>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,obyčejné"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,obyčejné"&amp;12Stránka &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D18"/>
+  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="19.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="17.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="19.72"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="0"/>
+      <c r="C14" s="0"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="0"/>
+      <c r="C15" s="0"/>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="0"/>
+      <c r="C16" s="0"/>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="0"/>
+      <c r="C17" s="0"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C18" s="5"/>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,obyčejné"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,obyčejné"&amp;12Stránka &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D18"/>
+  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="19.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="17.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="19.72"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="0"/>
+      <c r="C10" s="0"/>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="0"/>
+      <c r="C14" s="0"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="0"/>
+      <c r="C15" s="0"/>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="0"/>
+      <c r="C16" s="0"/>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="0"/>
+      <c r="C17" s="0"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C18" s="5"/>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,obyčejné"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,obyčejné"&amp;12Stránka &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D18"/>
+  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="19.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="17.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="19.72"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="0"/>
+      <c r="C10" s="0"/>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="0"/>
+      <c r="C14" s="0"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="0"/>
+      <c r="C15" s="0"/>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="0"/>
+      <c r="C16" s="0"/>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="0"/>
+      <c r="C17" s="0"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C18" s="5"/>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,obyčejné"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,obyčejné"&amp;12Stránka &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="19.79"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>182</v>
+      </c>
+      <c r="C4" s="0" t="s">
+        <v>226</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,obyčejné"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,obyčejné"&amp;12Stránka &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D26"/>
+  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="19.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="22.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="19.72"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>227</v>
+      </c>
+      <c r="C2" s="0" t="s">
+        <v>189</v>
+      </c>
+      <c r="D2" s="0" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>228</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>191</v>
+      </c>
+      <c r="D3" s="0" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>229</v>
+      </c>
+      <c r="C4" s="0" t="s">
+        <v>132</v>
+      </c>
+      <c r="D4" s="0" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>230</v>
+      </c>
+      <c r="C5" s="0" t="s">
+        <v>209</v>
+      </c>
+      <c r="D5" s="0" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>231</v>
+      </c>
+      <c r="C6" s="0" t="s">
+        <v>185</v>
+      </c>
+      <c r="D6" s="0" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>232</v>
+      </c>
+      <c r="C7" s="0" t="s">
+        <v>187</v>
+      </c>
+      <c r="D7" s="0" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>233</v>
+      </c>
+      <c r="C8" s="0" t="s">
+        <v>194</v>
+      </c>
+      <c r="D8" s="0" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="0" t="s">
+        <v>234</v>
+      </c>
+      <c r="C9" s="0" t="s">
+        <v>196</v>
+      </c>
+      <c r="D9" s="0" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="7"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="7"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="0"/>
+      <c r="C13" s="0"/>
+      <c r="D13" s="0"/>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="0"/>
+      <c r="C14" s="0"/>
+      <c r="D14" s="0"/>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="0"/>
+      <c r="C15" s="0"/>
+      <c r="D15" s="0"/>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="0"/>
+      <c r="C16" s="0"/>
+      <c r="D16" s="0"/>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="0"/>
+      <c r="C17" s="0"/>
+      <c r="D17" s="0"/>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="0"/>
+      <c r="C18" s="0"/>
+      <c r="D18" s="0"/>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="0"/>
+      <c r="C19" s="0"/>
+      <c r="D19" s="0"/>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="0"/>
+      <c r="C20" s="0"/>
+      <c r="D20" s="0"/>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="0"/>
+      <c r="C21" s="0"/>
+      <c r="D21" s="0"/>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="0"/>
+      <c r="C22" s="0"/>
+      <c r="D22" s="0"/>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="0"/>
+      <c r="C23" s="0"/>
+      <c r="D23" s="0"/>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="0"/>
+      <c r="C24" s="0"/>
+      <c r="D24" s="0"/>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B25" s="0"/>
+      <c r="C25" s="0"/>
+      <c r="D25" s="0"/>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="0"/>
+      <c r="C26" s="0"/>
+      <c r="D26" s="0"/>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,obyčejné"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,obyčejné"&amp;12Stránka &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="24.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="12.83"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>34</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/Manual/source/CZ/tab/connectors.xlsx
+++ b/Manual/source/CZ/tab/connectors.xlsx
@@ -5,18 +5,18 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="35"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="38"/>
   </bookViews>
   <sheets>
     <sheet name="rozcestnik" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="X1_24V_5pin_BCZ" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="X2_48_DC_1778065" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="X8_IO_22pin_BCZ" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="X10_CAN_4pin_BCZ" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="X8_IO_22pin_B2CF" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="X10_CAN_4pin_B2CF" sheetId="5" state="visible" r:id="rId7"/>
     <sheet name="LEDsigAx12" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="X5_FBE_12pin_BCZ" sheetId="7" state="visible" r:id="rId9"/>
-    <sheet name="X6_FB1_8pin_BCZ" sheetId="8" state="visible" r:id="rId10"/>
-    <sheet name="X7_FB2_8pin_BCZ" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="X5_FBE_12pin_B2CF" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="X6_FB1_8pin_B2CF" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="X7_FB2_8pin_B2CF" sheetId="9" state="visible" r:id="rId11"/>
     <sheet name="X3_M1_6pin_BLZP" sheetId="10" state="visible" r:id="rId12"/>
     <sheet name="X4_M2_6pin_BLZP" sheetId="11" state="visible" r:id="rId13"/>
     <sheet name="X1_24V_5pin_Microlock" sheetId="12" state="visible" r:id="rId14"/>
@@ -44,6 +44,10 @@
     <sheet name="X1_ACIN_PC5" sheetId="34" state="visible" r:id="rId36"/>
     <sheet name="X2_DC_8pin_PC5" sheetId="35" state="visible" r:id="rId37"/>
     <sheet name="X3_DO_4pin_BCZ" sheetId="36" state="visible" r:id="rId38"/>
+    <sheet name="X3_24V_BLF_2_5" sheetId="37" state="visible" r:id="rId39"/>
+    <sheet name="X5_DI_10pin_B2CF" sheetId="38" state="visible" r:id="rId40"/>
+    <sheet name="X10_DO_10pin_B2CF" sheetId="39" state="visible" r:id="rId41"/>
+    <sheet name="S1_SWITCH_CAN" sheetId="40" state="visible" r:id="rId42"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -55,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="738" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="809" uniqueCount="280">
   <si>
     <t xml:space="preserve">Toto je sešit se zdrojovými tabulkami popisu konektorů TGZ/TGS v češtině. Každý list odpovídá jednomu unikátnímu typu konektoru. Jelikož se často konektory v rámci TGZ opakují (typicky ty na řídicií desce), jsou zde jen jednou. Tj. Např. IO konektor 22pin weidmuller BCZ se používá pořád dokola, je zde tedy zanesen jen jednou jako „X8_IO_22pin_BCZ“</t>
   </si>
@@ -820,6 +824,117 @@
   </si>
   <si>
     <t xml:space="preserve">Signál „Error“ kontakt 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+PWR 24V</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vstup pro napájecí napětí 24V</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0,08 ~ 0,5 mm2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PWRCOM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vstup pro napájecí zem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IN1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IN2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IN3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IN4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IN5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IN6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IN7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IN8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IN9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Digitální vstup č. 9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IN10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Digitální vstup č. 10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OUT1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OUT2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OUT3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OUT4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OUT5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OUT6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OUT7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OUT8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OUTCOM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Společná zem DO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OUTPWR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Společné napájení DO 24V</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pozice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Funkce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nahoře</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vypnuto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAN není terminován</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dole</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zapnuto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAN je terminován</t>
   </si>
 </sst>
 </file>
@@ -3832,22 +3947,6 @@
         <v>154</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="0"/>
-      <c r="C14" s="0"/>
-    </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="0"/>
-      <c r="C15" s="0"/>
-    </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="0"/>
-      <c r="C16" s="0"/>
-    </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="0"/>
-      <c r="C17" s="0"/>
-    </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C18" s="5"/>
     </row>
@@ -3945,22 +4044,6 @@
         <v>154</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="0"/>
-      <c r="C14" s="0"/>
-    </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="0"/>
-      <c r="C15" s="0"/>
-    </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="0"/>
-      <c r="C16" s="0"/>
-    </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="0"/>
-      <c r="C17" s="0"/>
-    </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C18" s="5"/>
     </row>
@@ -4058,26 +4141,6 @@
         <v>222</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="0"/>
-      <c r="C10" s="0"/>
-    </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="0"/>
-      <c r="C14" s="0"/>
-    </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="0"/>
-      <c r="C15" s="0"/>
-    </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="0"/>
-      <c r="C16" s="0"/>
-    </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="0"/>
-      <c r="C17" s="0"/>
-    </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C18" s="5"/>
     </row>
@@ -4175,26 +4238,6 @@
         <v>222</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="0"/>
-      <c r="C10" s="0"/>
-    </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="0"/>
-      <c r="C14" s="0"/>
-    </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="0"/>
-      <c r="C15" s="0"/>
-    </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="0"/>
-      <c r="C16" s="0"/>
-    </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="0"/>
-      <c r="C17" s="0"/>
-    </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C18" s="5"/>
     </row>
@@ -4217,7 +4260,7 @@
   <dimension ref="A1:D4"/>
   <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="19.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="19.79"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4263,13 +4306,13 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>226</v>
       </c>
       <c r="D4" s="1" t="s">
@@ -4292,7 +4335,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="19.31"/>
@@ -4301,128 +4344,128 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+      <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="1" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+      <c r="A5" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" s="1" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
+      <c r="A6" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" s="1" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
+      <c r="A7" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="D7" s="0" t="s">
+      <c r="D7" s="1" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="n">
+      <c r="A8" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="C8" s="0" t="s">
+      <c r="C8" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="D8" s="0" t="s">
+      <c r="D8" s="1" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="n">
+      <c r="A9" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="C9" s="0" t="s">
+      <c r="C9" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="D9" s="0" t="s">
+      <c r="D9" s="1" t="s">
         <v>198</v>
       </c>
     </row>
@@ -4437,76 +4480,6 @@
       <c r="B11" s="7"/>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
-    </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="0"/>
-      <c r="C13" s="0"/>
-      <c r="D13" s="0"/>
-    </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="0"/>
-      <c r="C14" s="0"/>
-      <c r="D14" s="0"/>
-    </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="0"/>
-      <c r="C15" s="0"/>
-      <c r="D15" s="0"/>
-    </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="0"/>
-      <c r="C16" s="0"/>
-      <c r="D16" s="0"/>
-    </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="0"/>
-      <c r="C17" s="0"/>
-      <c r="D17" s="0"/>
-    </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="0"/>
-      <c r="C18" s="0"/>
-      <c r="D18" s="0"/>
-    </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="0"/>
-      <c r="C19" s="0"/>
-      <c r="D19" s="0"/>
-    </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="0"/>
-      <c r="C20" s="0"/>
-      <c r="D20" s="0"/>
-    </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="0"/>
-      <c r="C21" s="0"/>
-      <c r="D21" s="0"/>
-    </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="0"/>
-      <c r="C22" s="0"/>
-      <c r="D22" s="0"/>
-    </row>
-    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="0"/>
-      <c r="C23" s="0"/>
-      <c r="D23" s="0"/>
-    </row>
-    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="0"/>
-      <c r="C24" s="0"/>
-      <c r="D24" s="0"/>
-    </row>
-    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="0"/>
-      <c r="C25" s="0"/>
-      <c r="D25" s="0"/>
-    </row>
-    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="0"/>
-      <c r="C26" s="0"/>
-      <c r="D26" s="0"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -4614,6 +4587,409 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="26.98"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="12.83"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>245</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,obyčejné"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,obyčejné"&amp;12Stránka &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:C18"/>
+  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="17.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="0" width="11.53"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1"/>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C18" s="5"/>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,obyčejné"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,obyčejné"&amp;12Stránka &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:C18"/>
+  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="24.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="0" width="11.53"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1"/>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C18" s="5"/>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,obyčejné"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,obyčejné"&amp;12Stránka &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
@@ -4947,6 +5323,96 @@
       <c r="D23" s="1" t="s">
         <v>50</v>
       </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,obyčejné"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,obyčejné"&amp;12Stránka &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:C18"/>
+  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="24.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="0" width="11.53"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1"/>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1"/>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1"/>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1"/>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1"/>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1"/>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1"/>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C18" s="5"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/Manual/source/CZ/tab/connectors.xlsx
+++ b/Manual/source/CZ/tab/connectors.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="38"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="43"/>
   </bookViews>
   <sheets>
     <sheet name="rozcestnik" sheetId="1" state="visible" r:id="rId3"/>
@@ -48,6 +48,10 @@
     <sheet name="X5_DI_10pin_B2CF" sheetId="38" state="visible" r:id="rId40"/>
     <sheet name="X10_DO_10pin_B2CF" sheetId="39" state="visible" r:id="rId41"/>
     <sheet name="S1_SWITCH_CAN" sheetId="40" state="visible" r:id="rId42"/>
+    <sheet name="X1_24V_5pin_BCZ_TGM" sheetId="41" state="visible" r:id="rId43"/>
+    <sheet name="X5_FBE_12pin_B2CF_TGM" sheetId="42" state="visible" r:id="rId44"/>
+    <sheet name="X6_FB1_8pin_B2CF_TGM" sheetId="43" state="visible" r:id="rId45"/>
+    <sheet name="X7_FB2_8pin_B2CF_TGM" sheetId="44" state="visible" r:id="rId46"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -59,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="809" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="880" uniqueCount="286">
   <si>
     <t xml:space="preserve">Toto je sešit se zdrojovými tabulkami popisu konektorů TGZ/TGS v češtině. Každý list odpovídá jednomu unikátnímu typu konektoru. Jelikož se často konektory v rámci TGZ opakují (typicky ty na řídicií desce), jsou zde jen jednou. Tj. Např. IO konektor 22pin weidmuller BCZ se používá pořád dokola, je zde tedy zanesen jen jednou jako „X8_IO_22pin_BCZ“</t>
   </si>
@@ -935,6 +939,24 @@
   </si>
   <si>
     <t xml:space="preserve">CAN je terminován</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EI1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rozšířený vstup 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EI2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rozšířený vstup 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+24V napájení</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSI</t>
   </si>
 </sst>
 </file>
@@ -4692,7 +4714,7 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16.27"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="17.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="0" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4846,7 +4868,7 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16.27"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="24.1"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="0" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5345,74 +5367,561 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16.27"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="24.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="1" width="11.53"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1"/>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1"/>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1"/>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1"/>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1"/>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1"/>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1"/>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1"/>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C18" s="5"/>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,obyčejné"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,obyčejné"&amp;12Stránka &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultColWidth="11.72265625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="18.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="12.83"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,obyčejné"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,obyčejné"&amp;12Stránka &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:B13"/>
+  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="19.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16383" style="0" width="11.53"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,obyčejné"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,obyčejné"&amp;12Stránka &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:C18"/>
+  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="19.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="17.78"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="0" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>272</v>
+        <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>273</v>
+        <v>103</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>104</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
-        <v>274</v>
+      <c r="A2" s="1" t="n">
+        <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>275</v>
+        <v>109</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>276</v>
+        <v>113</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
-        <v>277</v>
+      <c r="A3" s="1" t="n">
+        <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>278</v>
+        <v>109</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>279</v>
+        <v>114</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1"/>
+      <c r="A4" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1"/>
+      <c r="A5" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1"/>
+      <c r="A6" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1"/>
+      <c r="A7" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1"/>
+      <c r="A8" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1"/>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1"/>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1"/>
-    </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1"/>
-    </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1"/>
+      <c r="A9" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C18" s="5"/>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,obyčejné"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,obyčejné"&amp;12Stránka &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:C18"/>
+  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="17.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="19.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="0" width="11.53"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="5"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/Manual/source/CZ/tab/connectors.xlsx
+++ b/Manual/source/CZ/tab/connectors.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="43"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="rozcestnik" sheetId="1" state="visible" r:id="rId3"/>
@@ -63,9 +63,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="880" uniqueCount="286">
-  <si>
-    <t xml:space="preserve">Toto je sešit se zdrojovými tabulkami popisu konektorů TGZ/TGS v češtině. Každý list odpovídá jednomu unikátnímu typu konektoru. Jelikož se často konektory v rámci TGZ opakují (typicky ty na řídicií desce), jsou zde jen jednou. Tj. Např. IO konektor 22pin weidmuller BCZ se používá pořád dokola, je zde tedy zanesen jen jednou jako „X8_IO_22pin_BCZ“</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1345" uniqueCount="327">
+  <si>
+    <t xml:space="preserve">Toto je sešit se zdrojovými tabulkami popisu konektorů TGZ/TGS v češtině. Každý list odpovídá jednomu unikátnímu typu konektoru. Jelikož se často konektory v rámci TGZ opakují (typicky ty na řídicií desce), jsou zde jen jednou. Tj. Např. IO konektor 22pin weidmuller B2CF se používá pořád dokola, je zde tedy zanesen jen jednou jako „X8_IO_22pin_B2CF“</t>
   </si>
   <si>
     <t xml:space="preserve">výrobce</t>
@@ -110,31 +110,31 @@
     <t xml:space="preserve">IO</t>
   </si>
   <si>
-    <t xml:space="preserve">#X8_IO_22pin_BCZ</t>
+    <t xml:space="preserve">#X8_IO_22pin_B2CF</t>
   </si>
   <si>
     <t xml:space="preserve">CAN</t>
   </si>
   <si>
-    <t xml:space="preserve">#X10_CAN_4pin_BCZ</t>
+    <t xml:space="preserve">#X10_CAN_4pin_B2CF</t>
   </si>
   <si>
     <t xml:space="preserve">FB1</t>
   </si>
   <si>
-    <t xml:space="preserve">#X6_FB1_8pin_BCZ</t>
+    <t xml:space="preserve">#X6_FB1_8pin_B2CF</t>
   </si>
   <si>
     <t xml:space="preserve">FB2</t>
   </si>
   <si>
-    <t xml:space="preserve">#X7_FB2_8pin_BCZ</t>
+    <t xml:space="preserve">#X7_FB2_8pin_B2CF</t>
   </si>
   <si>
     <t xml:space="preserve">FBE</t>
   </si>
   <si>
-    <t xml:space="preserve">#X5_FBE_12pin_BCZ</t>
+    <t xml:space="preserve">#X5_FBE_12pin_B2CF</t>
   </si>
   <si>
     <t xml:space="preserve">M1</t>
@@ -147,6 +147,129 @@
   </si>
   <si>
     <t xml:space="preserve">#X3_DCbus_2pin_pressfit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jen šrouby</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#X1_24V_5pin_BCZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#X3_M1_6pin_BLZP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#X4_M2_6pin_BLZP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#X2_48_DC_1778065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#X4_M1_6pin_SLS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">230VAC IN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#X2_PWR_10pin_BLZP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#X2_320_DC_1778078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#X4_M1_6pin_BLF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AC IN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#X2_PWR_12pin_BLZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#X3_M1_4pin_wago_2636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#X4_M2_4pin_wago_2636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#X2_D560DCbus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brzda 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#X14_BR1_4pin_LSF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brzda 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#X15_BR2_4pin_LSF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TGS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#X1_ACIN_PC5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DC OUT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#X2_DC_8pin_PC5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#X3_DO_4pin_BCZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TGM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mini</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#X3_24V_BLF_2_5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAN-SWITCH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#S1_SWITCH_CAN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#X5_DI_10pin_B2CF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#X10_DO_10pin_B2CF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ControlleR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#X1_24V_5pin_BCZ_TGM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#X6_FB1_8pin_B2CF_TGM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#X7_FB2_8pin_B2CF_TGM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#X5_FBE_12pin_B2CF_TGM</t>
   </si>
   <si>
     <t xml:space="preserve">Pin č.</t>
@@ -967,7 +1090,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="@"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -990,6 +1113,13 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+      <charset val="238"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <charset val="238"/>
     </font>
     <font>
@@ -1061,7 +1191,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="14">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1074,6 +1204,14 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1082,7 +1220,23 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="justify" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1277,11 +1431,11 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H138"/>
   <sheetFormatPr defaultColWidth="12.2734375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="13.82"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="14.59"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="17.95"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="31.81"/>
   </cols>
   <sheetData>
@@ -1377,151 +1531,2486 @@
       <c r="A9" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="1" t="s">
+      <c r="B9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="1" t="n">
+      <c r="D9" s="4" t="n">
         <v>48</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="E9" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="F9" s="3" t="n">
+      <c r="F9" s="5" t="n">
         <v>100</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="H9" s="4" t="s">
+      <c r="H9" s="6" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C10" s="1" t="s">
+      <c r="B10" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="1" t="n">
+      <c r="D10" s="4" t="n">
         <v>48</v>
       </c>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
       <c r="G10" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H10" s="4" t="s">
+      <c r="H10" s="7" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C11" s="1" t="s">
+      <c r="B11" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="1" t="n">
+      <c r="D11" s="4" t="n">
         <v>48</v>
       </c>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
       <c r="G11" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H11" s="4" t="s">
+      <c r="H11" s="6" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D12" s="1" t="n">
+      <c r="B12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" s="4" t="n">
         <v>48</v>
       </c>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
       <c r="G12" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="H12" s="4" t="s">
+      <c r="H12" s="6" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D13" s="1" t="n">
+      <c r="B13" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13" s="4" t="n">
         <v>48</v>
       </c>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
       <c r="G13" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H13" s="4" t="s">
+      <c r="H13" s="6" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D14" s="1" t="n">
+      <c r="B14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D14" s="4" t="n">
         <v>48</v>
       </c>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
       <c r="G14" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="H14" s="4" t="s">
+      <c r="H14" s="6" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D15" s="1" t="n">
+      <c r="B15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D15" s="4" t="n">
         <v>48</v>
       </c>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
       <c r="G15" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H15" s="4" t="s">
+      <c r="H15" s="6" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D16" s="1" t="n">
+      <c r="B16" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D16" s="4" t="n">
         <v>48</v>
       </c>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
       <c r="G16" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H16" s="4" t="s">
+      <c r="H16" s="6" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D17" s="1" t="n">
+      <c r="B17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D17" s="4" t="n">
         <v>48</v>
       </c>
-      <c r="E17" s="1" t="n">
+      <c r="E17" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="F17" s="1" t="n">
+      <c r="F17" s="5" t="n">
         <v>250</v>
       </c>
+      <c r="G17" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H21" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B25" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>300</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H25" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D26" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5"/>
+      <c r="G26" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H26" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D27" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H27" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B28" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D28" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="E28" s="5"/>
+      <c r="F28" s="5"/>
+      <c r="G28" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H28" s="6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D29" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="E29" s="5"/>
+      <c r="F29" s="5"/>
+      <c r="G29" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H29" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B30" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D30" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="E30" s="5"/>
+      <c r="F30" s="5"/>
+      <c r="G30" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H30" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B31" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D31" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="E31" s="5"/>
+      <c r="F31" s="5"/>
+      <c r="G31" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D32" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="E32" s="5"/>
+      <c r="F32" s="5"/>
+      <c r="G32" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D33" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="E33" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>450</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H33" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B34" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D34" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="E34" s="5"/>
+      <c r="F34" s="5"/>
+      <c r="G34" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H34" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D35" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="E35" s="5"/>
+      <c r="F35" s="5"/>
+      <c r="G35" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H35" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B36" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D36" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="E36" s="5"/>
+      <c r="F36" s="5"/>
+      <c r="G36" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H36" s="6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B37" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D37" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="E37" s="5"/>
+      <c r="F37" s="5"/>
+      <c r="G37" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H37" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B38" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D38" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="E38" s="5"/>
+      <c r="F38" s="5"/>
+      <c r="G38" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H38" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B39" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D39" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="E39" s="5"/>
+      <c r="F39" s="5"/>
+      <c r="G39" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B40" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D40" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="E40" s="5"/>
+      <c r="F40" s="5"/>
+      <c r="G40" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B41" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D41" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="E41" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="F41" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H41" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B42" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D42" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="E42" s="5"/>
+      <c r="F42" s="5"/>
+      <c r="G42" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H42" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B43" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D43" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="E43" s="5"/>
+      <c r="F43" s="5"/>
+      <c r="G43" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H43" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B44" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D44" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="E44" s="5"/>
+      <c r="F44" s="5"/>
+      <c r="G44" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H44" s="6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D45" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="E45" s="5"/>
+      <c r="F45" s="5"/>
+      <c r="G45" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H45" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B46" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D46" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="E46" s="5"/>
+      <c r="F46" s="5"/>
+      <c r="G46" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H46" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D47" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="E47" s="5"/>
+      <c r="F47" s="5"/>
+      <c r="G47" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H47" s="6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B48" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D48" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="E48" s="5"/>
+      <c r="F48" s="5"/>
+      <c r="G48" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H48" s="6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B49" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D49" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="E49" s="5"/>
+      <c r="F49" s="5"/>
+      <c r="G49" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H49" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B50" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>230</v>
+      </c>
+      <c r="E50" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F50" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H50" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B51" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>230</v>
+      </c>
+      <c r="E51" s="5"/>
+      <c r="F51" s="5"/>
+      <c r="G51" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H51" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B52" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>230</v>
+      </c>
+      <c r="E52" s="5"/>
+      <c r="F52" s="5"/>
+      <c r="G52" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H52" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B53" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>230</v>
+      </c>
+      <c r="E53" s="5"/>
+      <c r="F53" s="5"/>
+      <c r="G53" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H53" s="6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B54" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>230</v>
+      </c>
+      <c r="E54" s="5"/>
+      <c r="F54" s="5"/>
+      <c r="G54" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H54" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B55" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>230</v>
+      </c>
+      <c r="E55" s="5"/>
+      <c r="F55" s="5"/>
+      <c r="G55" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H55" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B56" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>230</v>
+      </c>
+      <c r="E56" s="5"/>
+      <c r="F56" s="5"/>
+      <c r="G56" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H56" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B57" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>230</v>
+      </c>
+      <c r="E57" s="5"/>
+      <c r="F57" s="5"/>
+      <c r="G57" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H57" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B58" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>320</v>
+      </c>
+      <c r="E58" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F58" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H58" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B59" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D59" s="3"/>
+      <c r="E59" s="5"/>
+      <c r="F59" s="5"/>
+      <c r="G59" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H59" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B60" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D60" s="3"/>
+      <c r="E60" s="5"/>
+      <c r="F60" s="5"/>
+      <c r="G60" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H60" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B61" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D61" s="3"/>
+      <c r="E61" s="5"/>
+      <c r="F61" s="5"/>
+      <c r="G61" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H61" s="6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B62" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D62" s="3"/>
+      <c r="E62" s="5"/>
+      <c r="F62" s="5"/>
+      <c r="G62" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H62" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B63" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D63" s="3"/>
+      <c r="E63" s="5"/>
+      <c r="F63" s="5"/>
+      <c r="G63" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H63" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B64" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D64" s="3"/>
+      <c r="E64" s="5"/>
+      <c r="F64" s="5"/>
+      <c r="G64" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H64" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B65" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D65" s="3"/>
+      <c r="E65" s="5"/>
+      <c r="F65" s="5"/>
+      <c r="G65" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H65" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B66" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D66" s="3"/>
+      <c r="E66" s="5"/>
+      <c r="F66" s="5"/>
+      <c r="G66" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H66" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B67" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>320</v>
+      </c>
+      <c r="E67" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F67" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H67" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B68" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D68" s="3"/>
+      <c r="E68" s="5"/>
+      <c r="F68" s="5"/>
+      <c r="G68" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H68" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B69" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D69" s="3"/>
+      <c r="E69" s="5"/>
+      <c r="F69" s="5"/>
+      <c r="G69" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H69" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B70" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D70" s="3"/>
+      <c r="E70" s="5"/>
+      <c r="F70" s="5"/>
+      <c r="G70" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H70" s="6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B71" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D71" s="3"/>
+      <c r="E71" s="5"/>
+      <c r="F71" s="5"/>
+      <c r="G71" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H71" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B72" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D72" s="3"/>
+      <c r="E72" s="5"/>
+      <c r="F72" s="5"/>
+      <c r="G72" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H72" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B73" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D73" s="3"/>
+      <c r="E73" s="5"/>
+      <c r="F73" s="5"/>
+      <c r="G73" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H73" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B74" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D74" s="3"/>
+      <c r="E74" s="5"/>
+      <c r="F74" s="5"/>
+      <c r="G74" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H74" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B75" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D75" s="3"/>
+      <c r="E75" s="5"/>
+      <c r="F75" s="5"/>
+      <c r="G75" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H75" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B76" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D76" s="3" t="n">
+        <v>400</v>
+      </c>
+      <c r="E76" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F76" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="G76" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H76" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B77" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D77" s="3"/>
+      <c r="E77" s="8"/>
+      <c r="F77" s="5"/>
+      <c r="G77" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H77" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B78" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D78" s="3"/>
+      <c r="E78" s="8"/>
+      <c r="F78" s="5"/>
+      <c r="G78" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H78" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B79" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D79" s="3"/>
+      <c r="E79" s="8"/>
+      <c r="F79" s="5"/>
+      <c r="G79" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H79" s="6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B80" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D80" s="3"/>
+      <c r="E80" s="8"/>
+      <c r="F80" s="5"/>
+      <c r="G80" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H80" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B81" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D81" s="3"/>
+      <c r="E81" s="8"/>
+      <c r="F81" s="5"/>
+      <c r="G81" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H81" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B82" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D82" s="3"/>
+      <c r="E82" s="8"/>
+      <c r="F82" s="5"/>
+      <c r="G82" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H82" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B83" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D83" s="3"/>
+      <c r="E83" s="8"/>
+      <c r="F83" s="5"/>
+      <c r="G83" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H83" s="6" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B84" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D84" s="3"/>
+      <c r="E84" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="F84" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="G84" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H84" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B85" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D85" s="3"/>
+      <c r="E85" s="8"/>
+      <c r="F85" s="5"/>
+      <c r="G85" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H85" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B86" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D86" s="3"/>
+      <c r="E86" s="8"/>
+      <c r="F86" s="5"/>
+      <c r="G86" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H86" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B87" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D87" s="3"/>
+      <c r="E87" s="8"/>
+      <c r="F87" s="5"/>
+      <c r="G87" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H87" s="6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B88" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D88" s="3"/>
+      <c r="E88" s="8"/>
+      <c r="F88" s="5"/>
+      <c r="G88" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H88" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B89" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D89" s="3"/>
+      <c r="E89" s="8"/>
+      <c r="F89" s="5"/>
+      <c r="G89" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H89" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B90" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D90" s="3"/>
+      <c r="E90" s="8"/>
+      <c r="F90" s="5"/>
+      <c r="G90" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H90" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B91" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D91" s="3"/>
+      <c r="E91" s="8"/>
+      <c r="F91" s="5"/>
+      <c r="G91" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H91" s="6" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B92" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D92" s="3"/>
+      <c r="E92" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F92" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="G92" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H92" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B93" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D93" s="3"/>
+      <c r="E93" s="8"/>
+      <c r="F93" s="5"/>
+      <c r="G93" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H93" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B94" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D94" s="3"/>
+      <c r="E94" s="8"/>
+      <c r="F94" s="5"/>
+      <c r="G94" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H94" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B95" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D95" s="3"/>
+      <c r="E95" s="8"/>
+      <c r="F95" s="5"/>
+      <c r="G95" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H95" s="6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B96" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D96" s="3"/>
+      <c r="E96" s="8"/>
+      <c r="F96" s="5"/>
+      <c r="G96" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H96" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B97" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D97" s="3"/>
+      <c r="E97" s="8"/>
+      <c r="F97" s="5"/>
+      <c r="G97" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H97" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B98" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D98" s="3"/>
+      <c r="E98" s="8"/>
+      <c r="F98" s="5"/>
+      <c r="G98" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H98" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B99" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D99" s="3"/>
+      <c r="E99" s="8"/>
+      <c r="F99" s="5"/>
+      <c r="G99" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H99" s="6" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B100" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D100" s="3"/>
+      <c r="E100" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="F100" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="G100" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H100" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B101" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D101" s="3"/>
+      <c r="E101" s="8"/>
+      <c r="F101" s="5"/>
+      <c r="G101" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H101" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B102" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D102" s="3"/>
+      <c r="E102" s="8"/>
+      <c r="F102" s="5"/>
+      <c r="G102" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H102" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B103" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D103" s="3"/>
+      <c r="E103" s="8"/>
+      <c r="F103" s="5"/>
+      <c r="G103" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H103" s="6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B104" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D104" s="3"/>
+      <c r="E104" s="8"/>
+      <c r="F104" s="5"/>
+      <c r="G104" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H104" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B105" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C105" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D105" s="3"/>
+      <c r="E105" s="8"/>
+      <c r="F105" s="5"/>
+      <c r="G105" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H105" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B106" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D106" s="3"/>
+      <c r="E106" s="8"/>
+      <c r="F106" s="5"/>
+      <c r="G106" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H106" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B107" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C107" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D107" s="3"/>
+      <c r="E107" s="8"/>
+      <c r="F107" s="5"/>
+      <c r="G107" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H107" s="6" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B108" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C108" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D108" s="8" t="n">
+        <v>560</v>
+      </c>
+      <c r="E108" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="F108" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="G108" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H108" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B109" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C109" s="3"/>
+      <c r="D109" s="8"/>
+      <c r="E109" s="5"/>
+      <c r="F109" s="5"/>
+      <c r="G109" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H109" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B110" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C110" s="3"/>
+      <c r="D110" s="8"/>
+      <c r="E110" s="5"/>
+      <c r="F110" s="5"/>
+      <c r="G110" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H110" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B111" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C111" s="3"/>
+      <c r="D111" s="8"/>
+      <c r="E111" s="5"/>
+      <c r="F111" s="5"/>
+      <c r="G111" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H111" s="6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B112" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C112" s="3"/>
+      <c r="D112" s="8"/>
+      <c r="E112" s="5"/>
+      <c r="F112" s="5"/>
+      <c r="G112" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H112" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B113" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C113" s="3"/>
+      <c r="D113" s="8"/>
+      <c r="E113" s="5"/>
+      <c r="F113" s="5"/>
+      <c r="G113" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H113" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B114" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C114" s="3"/>
+      <c r="D114" s="8"/>
+      <c r="E114" s="5"/>
+      <c r="F114" s="5"/>
+      <c r="G114" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H114" s="6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B115" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C115" s="3"/>
+      <c r="D115" s="8"/>
+      <c r="E115" s="5"/>
+      <c r="F115" s="5"/>
+      <c r="G115" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H115" s="6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B116" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C116" s="3"/>
+      <c r="D116" s="8"/>
+      <c r="E116" s="5"/>
+      <c r="F116" s="5"/>
+      <c r="G116" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H116" s="6" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B117" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C117" s="3"/>
+      <c r="D117" s="3"/>
+      <c r="E117" s="3"/>
+      <c r="F117" s="5"/>
+      <c r="G117" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H117" s="9" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B118" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C118" s="3"/>
+      <c r="D118" s="3"/>
+      <c r="E118" s="3"/>
+      <c r="F118" s="5"/>
+      <c r="G118" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H118" s="9" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B119" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="C119" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="D119" s="8" t="n">
+        <v>320</v>
+      </c>
+      <c r="E119" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F119" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="G119" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H119" s="9" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B120" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="C120" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="D120" s="8"/>
+      <c r="E120" s="8"/>
+      <c r="F120" s="4"/>
+      <c r="G120" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H120" s="9" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B121" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="C121" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="D121" s="8"/>
+      <c r="E121" s="8"/>
+      <c r="F121" s="4"/>
+      <c r="G121" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H121" s="9" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B122" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="C122" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="D122" s="8" t="n">
+        <v>560</v>
+      </c>
+      <c r="E122" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="F122" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="G122" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B123" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="C123" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="D123" s="8"/>
+      <c r="E123" s="8"/>
+      <c r="F123" s="4"/>
+      <c r="G123" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B124" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="C124" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="D124" s="8"/>
+      <c r="E124" s="8"/>
+      <c r="F124" s="4"/>
+      <c r="G124" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B125" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="C125" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="D125" s="8" t="n">
+        <v>560</v>
+      </c>
+      <c r="E125" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="F125" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="G125" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B126" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="C126" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="D126" s="8"/>
+      <c r="E126" s="8"/>
+      <c r="F126" s="4"/>
+      <c r="G126" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="127" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B127" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="C127" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="D127" s="8"/>
+      <c r="E127" s="8"/>
+      <c r="F127" s="4"/>
+      <c r="G127" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="128" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B128" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="C128" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="D128" s="10"/>
+      <c r="E128" s="10"/>
+      <c r="F128" s="10"/>
+      <c r="G128" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H128" s="9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="129" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B129" s="8"/>
+      <c r="C129" s="10"/>
+      <c r="D129" s="10"/>
+      <c r="E129" s="10"/>
+      <c r="F129" s="10"/>
+      <c r="G129" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H129" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B130" s="8"/>
+      <c r="C130" s="10"/>
+      <c r="D130" s="10"/>
+      <c r="E130" s="10"/>
+      <c r="F130" s="10"/>
+      <c r="G130" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="H130" s="9" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B131" s="8"/>
+      <c r="C131" s="10"/>
+      <c r="D131" s="10"/>
+      <c r="E131" s="10"/>
+      <c r="F131" s="10"/>
+      <c r="G131" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H131" s="9" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B132" s="8"/>
+      <c r="C132" s="10"/>
+      <c r="D132" s="10"/>
+      <c r="E132" s="10"/>
+      <c r="F132" s="10"/>
+      <c r="G132" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H132" s="9" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="133" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B133" s="8"/>
+      <c r="C133" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="D133" s="10"/>
+      <c r="E133" s="10"/>
+      <c r="F133" s="10"/>
+      <c r="G133" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H133" s="9" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B134" s="8"/>
+      <c r="C134" s="8"/>
+      <c r="D134" s="10"/>
+      <c r="E134" s="10"/>
+      <c r="F134" s="10"/>
+      <c r="G134" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H134" s="6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="135" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B135" s="8"/>
+      <c r="C135" s="8"/>
+      <c r="D135" s="10"/>
+      <c r="E135" s="10"/>
+      <c r="F135" s="10"/>
+      <c r="G135" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H135" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="136" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B136" s="8"/>
+      <c r="C136" s="8"/>
+      <c r="D136" s="10"/>
+      <c r="E136" s="10"/>
+      <c r="F136" s="10"/>
+      <c r="G136" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H136" s="6" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="137" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B137" s="8"/>
+      <c r="C137" s="8"/>
+      <c r="D137" s="10"/>
+      <c r="E137" s="10"/>
+      <c r="F137" s="10"/>
+      <c r="G137" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H137" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="138" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B138" s="8"/>
+      <c r="C138" s="8"/>
+      <c r="D138" s="10"/>
+      <c r="E138" s="10"/>
+      <c r="F138" s="10"/>
+      <c r="G138" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H138" s="6" t="s">
+        <v>68</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="49">
     <mergeCell ref="A1:H6"/>
+    <mergeCell ref="B9:B118"/>
+    <mergeCell ref="C9:C40"/>
+    <mergeCell ref="D9:D49"/>
     <mergeCell ref="E9:E16"/>
     <mergeCell ref="F9:F16"/>
+    <mergeCell ref="E17:E40"/>
+    <mergeCell ref="F17:F24"/>
+    <mergeCell ref="F25:F32"/>
+    <mergeCell ref="F33:F40"/>
+    <mergeCell ref="C41:C49"/>
+    <mergeCell ref="E41:E49"/>
+    <mergeCell ref="F41:F49"/>
+    <mergeCell ref="C50:C57"/>
+    <mergeCell ref="D50:D57"/>
+    <mergeCell ref="E50:E75"/>
+    <mergeCell ref="F50:F57"/>
+    <mergeCell ref="C58:C75"/>
+    <mergeCell ref="D58:D75"/>
+    <mergeCell ref="F58:F66"/>
+    <mergeCell ref="F67:F75"/>
+    <mergeCell ref="C76:C107"/>
+    <mergeCell ref="D76:D107"/>
+    <mergeCell ref="E76:E83"/>
+    <mergeCell ref="F76:F83"/>
+    <mergeCell ref="E84:E91"/>
+    <mergeCell ref="F84:F91"/>
+    <mergeCell ref="E92:E99"/>
+    <mergeCell ref="F92:F99"/>
+    <mergeCell ref="E100:E107"/>
+    <mergeCell ref="F100:F107"/>
+    <mergeCell ref="C108:C118"/>
+    <mergeCell ref="D108:D118"/>
+    <mergeCell ref="E108:E118"/>
+    <mergeCell ref="F108:F118"/>
+    <mergeCell ref="B119:B127"/>
+    <mergeCell ref="C119:C127"/>
+    <mergeCell ref="D119:D121"/>
+    <mergeCell ref="E119:E121"/>
+    <mergeCell ref="F119:F121"/>
+    <mergeCell ref="D122:D124"/>
+    <mergeCell ref="E122:E124"/>
+    <mergeCell ref="F122:F124"/>
+    <mergeCell ref="D125:D127"/>
+    <mergeCell ref="E125:E127"/>
+    <mergeCell ref="F125:F127"/>
+    <mergeCell ref="B128:B138"/>
+    <mergeCell ref="C128:F132"/>
+    <mergeCell ref="C133:F138"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="H9" location="X1_24V_5pin_Microlock!A1" display="#X1_24V_5pin_Microlock"/>
-    <hyperlink ref="H10" location="X8_IO_22pin_BCZ!A1" display="#X8_IO_22pin_BCZ"/>
-    <hyperlink ref="H11" location="X10_CAN_4pin_BCZ!A1" display="#X10_CAN_4pin_BCZ"/>
-    <hyperlink ref="H12" location="X6_FB1_8pin_BCZ!A1" display="#X6_FB1_8pin_BCZ"/>
-    <hyperlink ref="H13" location="X7_FB2_8pin_BCZ!A1" display="#X7_FB2_8pin_BCZ"/>
-    <hyperlink ref="H14" location="X5_FBE_12pin_BCZ!A1" display="#X5_FBE_12pin_BCZ"/>
+    <hyperlink ref="H10" location="X8_IO_22pin_B2CF!A1" display="#X8_IO_22pin_B2CF"/>
+    <hyperlink ref="H11" location="X10_CAN_4pin_B2CF!A1" display="#X10_CAN_4pin_B2CF"/>
+    <hyperlink ref="H12" location="X6_FB1_8pin_B2CF!A1" display="#X6_FB1_8pin_B2CF"/>
+    <hyperlink ref="H13" location="X7_FB2_8pin_B2CF!A1" display="#X7_FB2_8pin_B2CF"/>
+    <hyperlink ref="H14" location="X5_FBE_12pin_B2CF!A1" display="#X5_FBE_12pin_B2CF"/>
     <hyperlink ref="H15" location="X3_M1_3pin_pressfit!A1" display="#X3_M1_3pin_pressfit"/>
     <hyperlink ref="H16" location="X3_DCbus_2pin_pressfit!A1" display="#X3_DCbus_2pin_pressfit"/>
+    <hyperlink ref="H17" location="X1_24V_5pin_Microlock!A1" display="#X1_24V_5pin_Microlock"/>
+    <hyperlink ref="H18" location="X8_IO_22pin_B2CF!A1" display="#X8_IO_22pin_B2CF"/>
+    <hyperlink ref="H19" location="X10_CAN_4pin_B2CF!A1" display="#X10_CAN_4pin_B2CF"/>
+    <hyperlink ref="H20" location="X6_FB1_8pin_B2CF!A1" display="#X6_FB1_8pin_B2CF"/>
+    <hyperlink ref="H21" location="X7_FB2_8pin_B2CF!A1" display="#X7_FB2_8pin_B2CF"/>
+    <hyperlink ref="H22" location="X5_FBE_12pin_B2CF!A1" display="#X5_FBE_12pin_B2CF"/>
+    <hyperlink ref="H25" location="X1_24V_5pin_Microlock!A1" display="#X1_24V_5pin_Microlock"/>
+    <hyperlink ref="H26" location="X8_IO_22pin_B2CF!A1" display="#X8_IO_22pin_B2CF"/>
+    <hyperlink ref="H27" location="X10_CAN_4pin_B2CF!A1" display="#X10_CAN_4pin_B2CF"/>
+    <hyperlink ref="H28" location="X6_FB1_8pin_B2CF!A1" display="#X6_FB1_8pin_B2CF"/>
+    <hyperlink ref="H29" location="X7_FB2_8pin_B2CF!A1" display="#X7_FB2_8pin_B2CF"/>
+    <hyperlink ref="H30" location="X5_FBE_12pin_B2CF!A1" display="#X5_FBE_12pin_B2CF"/>
+    <hyperlink ref="H33" location="X1_24V_5pin_Microlock!A1" display="#X1_24V_5pin_Microlock"/>
+    <hyperlink ref="H34" location="X8_IO_22pin_B2CF!A1" display="#X8_IO_22pin_B2CF"/>
+    <hyperlink ref="H35" location="X10_CAN_4pin_B2CF!A1" display="#X10_CAN_4pin_B2CF"/>
+    <hyperlink ref="H36" location="X6_FB1_8pin_B2CF!A1" display="#X6_FB1_8pin_B2CF"/>
+    <hyperlink ref="H37" location="X7_FB2_8pin_B2CF!A1" display="#X7_FB2_8pin_B2CF"/>
+    <hyperlink ref="H38" location="X5_FBE_12pin_B2CF!A1" display="#X5_FBE_12pin_B2CF"/>
+    <hyperlink ref="H41" location="X1_24V_5pin_BCZ!A1" display="#X1_24V_5pin_BCZ"/>
+    <hyperlink ref="H42" location="X8_IO_22pin_B2CF!A1" display="#X8_IO_22pin_B2CF"/>
+    <hyperlink ref="H43" location="X10_CAN_4pin_B2CF!A1" display="#X10_CAN_4pin_B2CF"/>
+    <hyperlink ref="H44" location="X6_FB1_8pin_B2CF!A1" display="#X6_FB1_8pin_B2CF"/>
+    <hyperlink ref="H45" location="X7_FB2_8pin_B2CF!A1" display="#X7_FB2_8pin_B2CF"/>
+    <hyperlink ref="H46" location="X5_FBE_12pin_B2CF!A1" display="#X5_FBE_12pin_B2CF"/>
+    <hyperlink ref="H47" location="X3_M1_6pin_BLZP!A1" display="#X3_M1_6pin_BLZP"/>
+    <hyperlink ref="H48" location="X4_M2_6pin_BLZP!A1" display="#X4_M2_6pin_BLZP"/>
+    <hyperlink ref="H49" location="X2_48_DC_1778065!A1" display="#X2_48_DC_1778065"/>
+    <hyperlink ref="H50" location="X1_24V_5pin_BCZ!A1" display="#X1_24V_5pin_BCZ"/>
+    <hyperlink ref="H51" location="X8_IO_22pin_B2CF!A1" display="#X8_IO_22pin_B2CF"/>
+    <hyperlink ref="H52" location="X10_CAN_4pin_B2CF!A1" display="#X10_CAN_4pin_B2CF"/>
+    <hyperlink ref="H53" location="X6_FB1_8pin_B2CF!A1" display="#X6_FB1_8pin_B2CF"/>
+    <hyperlink ref="H54" location="X7_FB2_8pin_B2CF!A1" display="#X7_FB2_8pin_B2CF"/>
+    <hyperlink ref="H55" location="X5_FBE_12pin_B2CF!A1" display="#X5_FBE_12pin_B2CF"/>
+    <hyperlink ref="H56" location="X4_M1_6pin_SLS!A1" display="#X4_M1_6pin_SLS"/>
+    <hyperlink ref="H57" location="X2_PWR_10pin_BLZP!A1" display="#X2_PWR_10pin_BLZP"/>
+    <hyperlink ref="H58" location="X1_24V_5pin_BCZ!A1" display="#X1_24V_5pin_BCZ"/>
+    <hyperlink ref="H59" location="X8_IO_22pin_B2CF!A1" display="#X8_IO_22pin_B2CF"/>
+    <hyperlink ref="H60" location="X10_CAN_4pin_B2CF!A1" display="#X10_CAN_4pin_B2CF"/>
+    <hyperlink ref="H61" location="X6_FB1_8pin_B2CF!A1" display="#X6_FB1_8pin_B2CF"/>
+    <hyperlink ref="H62" location="X7_FB2_8pin_B2CF!A1" display="#X7_FB2_8pin_B2CF"/>
+    <hyperlink ref="H63" location="X5_FBE_12pin_B2CF!A1" display="#X5_FBE_12pin_B2CF"/>
+    <hyperlink ref="H64" location="X4_M1_6pin_SLS!A1" display="#X4_M1_6pin_SLS"/>
+    <hyperlink ref="H65" location="X4_M1_6pin_SLS!A1" display="#X4_M1_6pin_SLS"/>
+    <hyperlink ref="H66" location="X2_320_DC_1778078!A1" display="#X2_320_DC_1778078"/>
+    <hyperlink ref="H67" location="X1_24V_5pin_BCZ!A1" display="#X1_24V_5pin_BCZ"/>
+    <hyperlink ref="H68" location="X8_IO_22pin_B2CF!A1" display="#X8_IO_22pin_B2CF"/>
+    <hyperlink ref="H69" location="X10_CAN_4pin_B2CF!A1" display="#X10_CAN_4pin_B2CF"/>
+    <hyperlink ref="H70" location="X6_FB1_8pin_B2CF!A1" display="#X6_FB1_8pin_B2CF"/>
+    <hyperlink ref="H71" location="X7_FB2_8pin_B2CF!A1" display="#X7_FB2_8pin_B2CF"/>
+    <hyperlink ref="H72" location="X5_FBE_12pin_B2CF!A1" display="#X5_FBE_12pin_B2CF"/>
+    <hyperlink ref="H73" location="X4_M1_6pin_SLS!A1" display="#X4_M1_6pin_SLS"/>
+    <hyperlink ref="H74" location="X4_M1_6pin_SLS!A1" display="#X4_M1_6pin_SLS"/>
+    <hyperlink ref="H75" location="X2_320_DC_1778078!A1" display="#X2_320_DC_1778078"/>
+    <hyperlink ref="H76" location="X1_24V_5pin_BCZ!A1" display="#X1_24V_5pin_BCZ"/>
+    <hyperlink ref="H77" location="X8_IO_22pin_B2CF!A1" display="#X8_IO_22pin_B2CF"/>
+    <hyperlink ref="H78" location="X10_CAN_4pin_B2CF!A1" display="#X10_CAN_4pin_B2CF"/>
+    <hyperlink ref="H79" location="X6_FB1_8pin_B2CF!A1" display="#X6_FB1_8pin_B2CF"/>
+    <hyperlink ref="H80" location="X7_FB2_8pin_B2CF!A1" display="#X7_FB2_8pin_B2CF"/>
+    <hyperlink ref="H81" location="X5_FBE_12pin_B2CF!A1" display="#X5_FBE_12pin_B2CF"/>
+    <hyperlink ref="H82" location="X4_M1_6pin_BLF!A1" display="#X4_M1_6pin_BLF"/>
+    <hyperlink ref="H83" location="X2_PWR_12pin_BLZ!A1" display="#X2_PWR_12pin_BLZ"/>
+    <hyperlink ref="H84" location="X1_24V_5pin_BCZ!A1" display="#X1_24V_5pin_BCZ"/>
+    <hyperlink ref="H85" location="X8_IO_22pin_B2CF!A1" display="#X8_IO_22pin_B2CF"/>
+    <hyperlink ref="H86" location="X10_CAN_4pin_B2CF!A1" display="#X10_CAN_4pin_B2CF"/>
+    <hyperlink ref="H87" location="X6_FB1_8pin_B2CF!A1" display="#X6_FB1_8pin_B2CF"/>
+    <hyperlink ref="H88" location="X7_FB2_8pin_B2CF!A1" display="#X7_FB2_8pin_B2CF"/>
+    <hyperlink ref="H89" location="X5_FBE_12pin_B2CF!A1" display="#X5_FBE_12pin_B2CF"/>
+    <hyperlink ref="H90" location="X4_M1_6pin_BLF!A1" display="#X4_M1_6pin_BLF"/>
+    <hyperlink ref="H91" location="X2_PWR_12pin_BLZ!A1" display="#X2_PWR_12pin_BLZ"/>
+    <hyperlink ref="H92" location="X1_24V_5pin_BCZ!A1" display="#X1_24V_5pin_BCZ"/>
+    <hyperlink ref="H93" location="X8_IO_22pin_B2CF!A1" display="#X8_IO_22pin_B2CF"/>
+    <hyperlink ref="H94" location="X10_CAN_4pin_B2CF!A1" display="#X10_CAN_4pin_B2CF"/>
+    <hyperlink ref="H95" location="X6_FB1_8pin_B2CF!A1" display="#X6_FB1_8pin_B2CF"/>
+    <hyperlink ref="H96" location="X7_FB2_8pin_B2CF!A1" display="#X7_FB2_8pin_B2CF"/>
+    <hyperlink ref="H97" location="X5_FBE_12pin_B2CF!A1" display="#X5_FBE_12pin_B2CF"/>
+    <hyperlink ref="H98" location="X4_M1_6pin_BLF!A1" display="#X4_M1_6pin_BLF"/>
+    <hyperlink ref="H99" location="X2_PWR_12pin_BLZ!A1" display="#X2_PWR_12pin_BLZ"/>
+    <hyperlink ref="H100" location="X1_24V_5pin_BCZ!A1" display="#X1_24V_5pin_BCZ"/>
+    <hyperlink ref="H101" location="X8_IO_22pin_B2CF!A1" display="#X8_IO_22pin_B2CF"/>
+    <hyperlink ref="H102" location="X10_CAN_4pin_B2CF!A1" display="#X10_CAN_4pin_B2CF"/>
+    <hyperlink ref="H103" location="X6_FB1_8pin_B2CF!A1" display="#X6_FB1_8pin_B2CF"/>
+    <hyperlink ref="H104" location="X7_FB2_8pin_B2CF!A1" display="#X7_FB2_8pin_B2CF"/>
+    <hyperlink ref="H105" location="X5_FBE_12pin_B2CF!A1" display="#X5_FBE_12pin_B2CF"/>
+    <hyperlink ref="H106" location="X4_M1_6pin_BLF!A1" display="#X4_M1_6pin_BLF"/>
+    <hyperlink ref="H107" location="X2_PWR_12pin_BLZ!A1" display="#X2_PWR_12pin_BLZ"/>
+    <hyperlink ref="H108" location="X1_24V_5pin_BCZ!A1" display="#X1_24V_5pin_BCZ"/>
+    <hyperlink ref="H109" location="X8_IO_22pin_B2CF!A1" display="#X8_IO_22pin_B2CF"/>
+    <hyperlink ref="H110" location="X10_CAN_4pin_B2CF!A1" display="#X10_CAN_4pin_B2CF"/>
+    <hyperlink ref="H111" location="X6_FB1_8pin_B2CF!A1" display="#X6_FB1_8pin_B2CF"/>
+    <hyperlink ref="H112" location="X7_FB2_8pin_B2CF!A1" display="#X7_FB2_8pin_B2CF"/>
+    <hyperlink ref="H113" location="X5_FBE_12pin_B2CF!A1" display="#X5_FBE_12pin_B2CF"/>
+    <hyperlink ref="H114" location="X3_M1_4pin_wago_2636!A1" display="#X3_M1_4pin_wago_2636"/>
+    <hyperlink ref="H115" location="X4_M2_4pin_wago_2636!A1" display="#X4_M2_4pin_wago_2636"/>
+    <hyperlink ref="H116" location="X2_D560DCbus!A1" display="#X2_D560DCbus"/>
+    <hyperlink ref="H117" location="X14_BR1_4pin_LSF!A1" display="#X14_BR1_4pin_LSF"/>
+    <hyperlink ref="H118" location="X15_BR2_4pin_LSF!A1" display="#X15_BR2_4pin_LSF"/>
+    <hyperlink ref="H119" location="X1_ACIN_PC5!A1" display="#X1_ACIN_PC5"/>
+    <hyperlink ref="H120" location="X2_DC_8pin_PC5!A1" display="#X2_DC_8pin_PC5"/>
+    <hyperlink ref="H121" location="X3_DO_4pin_BCZ!A1" display="#X3_DO_4pin_BCZ"/>
+    <hyperlink ref="H128" location="X3_24V_BLF_2_5!A1" display="#X3_24V_BLF_2_5"/>
+    <hyperlink ref="H129" location="X10_CAN_4pin_B2CF!A1" display="#X10_CAN_4pin_B2CF"/>
+    <hyperlink ref="H130" location="S1_SWITCH_CAN!A1" display="#S1_SWITCH_CAN"/>
+    <hyperlink ref="H131" location="X5_DI_10pin_B2CF!A1" display="#X5_DI_10pin_B2CF"/>
+    <hyperlink ref="H132" location="X10_DO_10pin_B2CF!A1" display="#X10_DO_10pin_B2CF"/>
+    <hyperlink ref="H133" location="X1_24V_5pin_BCZ_TGM!A1" display="#X1_24V_5pin_BCZ_TGM"/>
+    <hyperlink ref="H134" location="X10_CAN_4pin_B2CF!A1" display="#X10_CAN_4pin_B2CF"/>
+    <hyperlink ref="H135" location="X8_IO_22pin_B2CF!A1" display="#X8_IO_22pin_B2CF"/>
+    <hyperlink ref="H136" location="X6_FB1_8pin_B2CF_TGM!A1" display="#X6_FB1_8pin_B2CF_TGM"/>
+    <hyperlink ref="H137" location="X7_FB2_8pin_B2CF_TGM!A1" display="#X7_FB2_8pin_B2CF_TGM"/>
+    <hyperlink ref="H138" location="X5_FBE_12pin_B2CF_TGM!A1" display="#X5_FBE_12pin_B2CF_TGM"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
@@ -1548,16 +4037,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>71</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>31</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1565,13 +4054,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>126</v>
+        <v>167</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>127</v>
+        <v>168</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>128</v>
+        <v>169</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1579,13 +4068,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>129</v>
+        <v>170</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>130</v>
+        <v>171</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>128</v>
+        <v>169</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1593,13 +4082,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>131</v>
+        <v>172</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>132</v>
+        <v>173</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>128</v>
+        <v>169</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1607,13 +4096,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>133</v>
+        <v>174</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>134</v>
+        <v>175</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>128</v>
+        <v>169</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1621,13 +4110,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>135</v>
+        <v>176</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>136</v>
+        <v>177</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>128</v>
+        <v>169</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1635,17 +4124,17 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>137</v>
+        <v>178</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>138</v>
+        <v>179</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>128</v>
+        <v>169</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C18" s="5"/>
+      <c r="C18" s="11"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -1673,16 +4162,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>71</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>31</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1690,13 +4179,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>126</v>
+        <v>167</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>127</v>
+        <v>168</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>128</v>
+        <v>169</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1704,13 +4193,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>129</v>
+        <v>170</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>130</v>
+        <v>171</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>128</v>
+        <v>169</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1718,13 +4207,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>131</v>
+        <v>172</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>132</v>
+        <v>173</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>128</v>
+        <v>169</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1732,13 +4221,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>133</v>
+        <v>174</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>134</v>
+        <v>175</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>128</v>
+        <v>169</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1746,13 +4235,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>135</v>
+        <v>176</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>136</v>
+        <v>177</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>128</v>
+        <v>169</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1760,17 +4249,17 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>137</v>
+        <v>178</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>138</v>
+        <v>179</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>128</v>
+        <v>169</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C18" s="5"/>
+      <c r="C18" s="11"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -1798,16 +4287,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>71</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>31</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1815,13 +4304,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>32</v>
+        <v>73</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>33</v>
+        <v>74</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>139</v>
+        <v>180</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1829,13 +4318,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>35</v>
+        <v>76</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>139</v>
+        <v>180</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1843,13 +4332,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>37</v>
+        <v>78</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>139</v>
+        <v>180</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1857,13 +4346,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>40</v>
+        <v>81</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>139</v>
+        <v>180</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1871,13 +4360,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>42</v>
+        <v>83</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>139</v>
+        <v>180</v>
       </c>
     </row>
   </sheetData>
@@ -1906,16 +4395,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>71</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>140</v>
+        <v>181</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1923,13 +4412,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>46</v>
+        <v>87</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>141</v>
+        <v>182</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>142</v>
+        <v>183</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1937,17 +4426,17 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>43</v>
+        <v>84</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>143</v>
+        <v>184</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>142</v>
+        <v>183</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C18" s="5"/>
+      <c r="C18" s="11"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -1975,16 +4464,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>71</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>140</v>
+        <v>181</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1992,13 +4481,13 @@
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>133</v>
+        <v>174</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>144</v>
+        <v>185</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>142</v>
+        <v>183</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2006,13 +4495,13 @@
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>135</v>
+        <v>176</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>145</v>
+        <v>186</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>142</v>
+        <v>183</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2020,17 +4509,17 @@
         <v>5</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>137</v>
+        <v>178</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>146</v>
+        <v>187</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>142</v>
+        <v>183</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C18" s="5"/>
+      <c r="C18" s="11"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -2058,16 +4547,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>71</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>31</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2075,13 +4564,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>147</v>
+        <v>188</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>127</v>
+        <v>168</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>139</v>
+        <v>180</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2089,13 +4578,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>148</v>
+        <v>189</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>130</v>
+        <v>171</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>139</v>
+        <v>180</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2103,13 +4592,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>149</v>
+        <v>190</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>150</v>
+        <v>191</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>139</v>
+        <v>180</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2117,13 +4606,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>151</v>
+        <v>192</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>152</v>
+        <v>193</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>139</v>
+        <v>180</v>
       </c>
     </row>
   </sheetData>
@@ -2152,16 +4641,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>71</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>31</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2169,13 +4658,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>131</v>
+        <v>172</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>153</v>
+        <v>194</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>154</v>
+        <v>195</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2183,13 +4672,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>46</v>
+        <v>87</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>141</v>
+        <v>182</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>154</v>
+        <v>195</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2197,17 +4686,17 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>43</v>
+        <v>84</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>143</v>
+        <v>184</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>154</v>
+        <v>195</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C18" s="5"/>
+      <c r="C18" s="11"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -2235,16 +4724,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>71</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>31</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2252,13 +4741,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>131</v>
+        <v>172</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>153</v>
+        <v>194</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>155</v>
+        <v>196</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2266,13 +4755,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>133</v>
+        <v>174</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>144</v>
+        <v>185</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>155</v>
+        <v>196</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2280,13 +4769,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>135</v>
+        <v>176</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>145</v>
+        <v>186</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>155</v>
+        <v>196</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2294,17 +4783,17 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>137</v>
+        <v>178</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>146</v>
+        <v>187</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>155</v>
+        <v>196</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C18" s="5"/>
+      <c r="C18" s="11"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -2332,16 +4821,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>71</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>31</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2349,13 +4838,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>131</v>
+        <v>172</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>153</v>
+        <v>194</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>155</v>
+        <v>196</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2363,13 +4852,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>133</v>
+        <v>174</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>144</v>
+        <v>185</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>155</v>
+        <v>196</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2377,13 +4866,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>135</v>
+        <v>176</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>145</v>
+        <v>186</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>155</v>
+        <v>196</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2391,17 +4880,17 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>137</v>
+        <v>178</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>146</v>
+        <v>187</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>155</v>
+        <v>196</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C18" s="5"/>
+      <c r="C18" s="11"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -2429,30 +4918,30 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>71</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>31</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="6" t="s">
-        <v>156</v>
+      <c r="B2" s="12" t="s">
+        <v>197</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>157</v>
+        <v>198</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>158</v>
+        <v>199</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2464,10 +4953,10 @@
         <v>-B2</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>159</v>
+        <v>200</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>158</v>
+        <v>199</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2475,13 +4964,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>147</v>
+        <v>188</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>160</v>
+        <v>201</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>158</v>
+        <v>199</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2489,45 +4978,45 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>148</v>
+        <v>189</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>161</v>
+        <v>202</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>158</v>
+        <v>199</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="6" t="s">
-        <v>162</v>
+      <c r="B6" s="12" t="s">
+        <v>203</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>163</v>
+        <v>204</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>158</v>
+        <v>199</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="6" t="s">
-        <v>164</v>
+      <c r="B7" s="12" t="s">
+        <v>205</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>165</v>
+        <v>206</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>158</v>
+        <v>199</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C18" s="5"/>
+      <c r="C18" s="11"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -2555,16 +5044,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>71</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>31</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2572,13 +5061,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>32</v>
+        <v>73</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>33</v>
+        <v>74</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>34</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2586,13 +5075,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>35</v>
+        <v>76</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>34</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2600,13 +5089,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>37</v>
+        <v>78</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>34</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2614,13 +5103,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>39</v>
+        <v>80</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>40</v>
+        <v>81</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>34</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2628,13 +5117,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>42</v>
+        <v>83</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>34</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -2664,16 +5153,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>71</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>31</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2681,13 +5170,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>37</v>
+        <v>78</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>166</v>
+        <v>207</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>167</v>
+        <v>208</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2695,13 +5184,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>168</v>
+        <v>209</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>169</v>
+        <v>210</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>167</v>
+        <v>208</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2709,13 +5198,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>42</v>
+        <v>83</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>167</v>
+        <v>208</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2723,13 +5212,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>32</v>
+        <v>73</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>33</v>
+        <v>74</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>167</v>
+        <v>208</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2737,13 +5226,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>35</v>
+        <v>76</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>167</v>
+        <v>208</v>
       </c>
     </row>
   </sheetData>
@@ -2773,16 +5262,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>71</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>31</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2790,13 +5279,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>37</v>
+        <v>78</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>170</v>
+        <v>211</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>167</v>
+        <v>208</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2804,13 +5293,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>171</v>
+        <v>212</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>172</v>
+        <v>213</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>167</v>
+        <v>208</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2818,13 +5307,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>148</v>
+        <v>189</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>173</v>
+        <v>214</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>167</v>
+        <v>208</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2832,13 +5321,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>147</v>
+        <v>188</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>174</v>
+        <v>215</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>167</v>
+        <v>208</v>
       </c>
     </row>
   </sheetData>
@@ -2868,16 +5357,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>71</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>31</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2885,13 +5374,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>95</v>
+        <v>136</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>175</v>
+        <v>216</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>167</v>
+        <v>208</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2899,13 +5388,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>95</v>
+        <v>136</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>175</v>
+        <v>216</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>167</v>
+        <v>208</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2913,13 +5402,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>95</v>
+        <v>136</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>175</v>
+        <v>216</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>167</v>
+        <v>208</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2927,13 +5416,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>176</v>
+        <v>217</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>167</v>
+        <v>208</v>
       </c>
     </row>
   </sheetData>
@@ -2963,16 +5452,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>71</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>31</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2980,13 +5469,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>177</v>
+        <v>218</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>178</v>
+        <v>219</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>167</v>
+        <v>208</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2994,13 +5483,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>177</v>
+        <v>218</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>178</v>
+        <v>219</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>167</v>
+        <v>208</v>
       </c>
     </row>
   </sheetData>
@@ -3029,16 +5518,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>71</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>31</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3046,13 +5535,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>126</v>
+        <v>167</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>127</v>
+        <v>168</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>179</v>
+        <v>220</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3060,13 +5549,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>129</v>
+        <v>170</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>130</v>
+        <v>171</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>179</v>
+        <v>220</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3074,13 +5563,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>131</v>
+        <v>172</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>132</v>
+        <v>173</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>179</v>
+        <v>220</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3088,13 +5577,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>133</v>
+        <v>174</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>134</v>
+        <v>175</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>179</v>
+        <v>220</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3102,13 +5591,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>135</v>
+        <v>176</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>136</v>
+        <v>177</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>179</v>
+        <v>220</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3116,17 +5605,17 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>137</v>
+        <v>178</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>138</v>
+        <v>179</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>179</v>
+        <v>220</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C18" s="5"/>
+      <c r="C18" s="11"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -3153,161 +5642,161 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>31</v>
+      <c r="A1" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="7" t="n">
+      <c r="A2" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>128</v>
+      <c r="B2" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="D2" s="13" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="7" t="n">
+      <c r="A3" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>128</v>
+      <c r="B3" s="13" t="s">
+        <v>221</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>222</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="n">
+      <c r="A4" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>128</v>
+      <c r="B4" s="13" t="s">
+        <v>223</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>224</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7" t="n">
+      <c r="A5" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="7" t="s">
-        <v>184</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>128</v>
+      <c r="B5" s="13" t="s">
+        <v>225</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>226</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7" t="n">
+      <c r="A6" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>187</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>128</v>
+      <c r="B6" s="13" t="s">
+        <v>227</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>228</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7" t="n">
+      <c r="A7" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>128</v>
+      <c r="B7" s="13" t="s">
+        <v>229</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>230</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7" t="n">
+      <c r="A8" s="13" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>128</v>
+      <c r="B8" s="13" t="s">
+        <v>231</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>232</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="n">
+      <c r="A9" s="13" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="7" t="s">
-        <v>192</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>128</v>
+      <c r="B9" s="13" t="s">
+        <v>233</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="7" t="n">
+      <c r="A10" s="13" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>194</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>128</v>
+      <c r="B10" s="13" t="s">
+        <v>234</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>235</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>196</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>128</v>
+      <c r="A11" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>236</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>237</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C18" s="5"/>
+      <c r="C18" s="11"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -3333,16 +5822,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>71</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>31</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3350,13 +5839,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>43</v>
+        <v>84</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>197</v>
+        <v>238</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>198</v>
+        <v>239</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3364,13 +5853,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>46</v>
+        <v>87</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>47</v>
+        <v>88</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>198</v>
+        <v>239</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3378,13 +5867,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>131</v>
+        <v>172</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>132</v>
+        <v>173</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>198</v>
+        <v>239</v>
       </c>
     </row>
   </sheetData>
@@ -3413,16 +5902,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>71</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>31</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3430,13 +5919,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>126</v>
+        <v>167</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>127</v>
+        <v>168</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>199</v>
+        <v>240</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3444,13 +5933,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>129</v>
+        <v>170</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>130</v>
+        <v>171</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>199</v>
+        <v>240</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3458,13 +5947,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>131</v>
+        <v>172</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>132</v>
+        <v>173</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>199</v>
+        <v>240</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3472,13 +5961,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>133</v>
+        <v>174</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>134</v>
+        <v>175</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>199</v>
+        <v>240</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3486,13 +5975,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>135</v>
+        <v>176</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>136</v>
+        <v>177</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>199</v>
+        <v>240</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3500,17 +5989,17 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>137</v>
+        <v>178</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>138</v>
+        <v>179</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>199</v>
+        <v>240</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C18" s="5"/>
+      <c r="C18" s="11"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -3538,16 +6027,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>71</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>31</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3555,13 +6044,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>131</v>
+        <v>172</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>132</v>
+        <v>173</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>128</v>
+        <v>169</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3569,13 +6058,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>200</v>
+        <v>241</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>201</v>
+        <v>242</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>128</v>
+        <v>169</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3583,13 +6072,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>202</v>
+        <v>243</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>203</v>
+        <v>244</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>128</v>
+        <v>169</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3597,13 +6086,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>204</v>
+        <v>245</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>205</v>
+        <v>246</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>128</v>
+        <v>169</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3611,13 +6100,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>206</v>
+        <v>247</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>207</v>
+        <v>248</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>128</v>
+        <v>169</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3625,13 +6114,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>208</v>
+        <v>249</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>209</v>
+        <v>250</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>128</v>
+        <v>169</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3639,13 +6128,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>210</v>
+        <v>251</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>211</v>
+        <v>252</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>128</v>
+        <v>169</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3653,13 +6142,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>188</v>
+        <v>229</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>189</v>
+        <v>230</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>128</v>
+        <v>169</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3667,13 +6156,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>190</v>
+        <v>231</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>191</v>
+        <v>232</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>128</v>
+        <v>169</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3681,13 +6170,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>192</v>
+        <v>233</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>132</v>
+        <v>173</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>128</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3695,13 +6184,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>212</v>
+        <v>253</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>213</v>
+        <v>254</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>128</v>
+        <v>169</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3709,13 +6198,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>214</v>
+        <v>255</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>215</v>
+        <v>256</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>128</v>
+        <v>169</v>
       </c>
     </row>
   </sheetData>
@@ -3744,16 +6233,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>71</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>31</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3761,13 +6250,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>216</v>
+        <v>257</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>217</v>
+        <v>258</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>218</v>
+        <v>259</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3775,13 +6264,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>219</v>
+        <v>260</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>220</v>
+        <v>261</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>218</v>
+        <v>259</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3835,16 +6324,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>71</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>31</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3852,13 +6341,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>43</v>
+        <v>84</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>44</v>
+        <v>85</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>45</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3866,13 +6355,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>46</v>
+        <v>87</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>47</v>
+        <v>88</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>45</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -3901,16 +6390,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>71</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>31</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3918,13 +6407,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>133</v>
+        <v>174</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>144</v>
+        <v>185</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>154</v>
+        <v>195</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3932,13 +6421,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>135</v>
+        <v>176</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>145</v>
+        <v>186</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>154</v>
+        <v>195</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3946,13 +6435,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>137</v>
+        <v>178</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>146</v>
+        <v>187</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>154</v>
+        <v>195</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3960,17 +6449,17 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>131</v>
+        <v>172</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>153</v>
+        <v>194</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>154</v>
+        <v>195</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C18" s="5"/>
+      <c r="C18" s="11"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -3998,16 +6487,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>71</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>31</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4015,13 +6504,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>133</v>
+        <v>174</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>144</v>
+        <v>185</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>154</v>
+        <v>195</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4029,13 +6518,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>135</v>
+        <v>176</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>145</v>
+        <v>186</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>154</v>
+        <v>195</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4043,13 +6532,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>137</v>
+        <v>178</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>146</v>
+        <v>187</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>154</v>
+        <v>195</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4057,17 +6546,17 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>131</v>
+        <v>172</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>153</v>
+        <v>194</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>154</v>
+        <v>195</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C18" s="5"/>
+      <c r="C18" s="11"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -4095,16 +6584,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>71</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>31</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4112,13 +6601,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>126</v>
+        <v>167</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>221</v>
+        <v>262</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>222</v>
+        <v>263</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4126,13 +6615,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>129</v>
+        <v>170</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>223</v>
+        <v>264</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>222</v>
+        <v>263</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4140,13 +6629,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>224</v>
+        <v>265</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>215</v>
+        <v>256</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>222</v>
+        <v>263</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4154,17 +6643,17 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>225</v>
+        <v>266</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>213</v>
+        <v>254</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>222</v>
+        <v>263</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C18" s="5"/>
+      <c r="C18" s="11"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -4192,16 +6681,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>71</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>31</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4209,13 +6698,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>126</v>
+        <v>167</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>221</v>
+        <v>262</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>222</v>
+        <v>263</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4223,13 +6712,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>129</v>
+        <v>170</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>223</v>
+        <v>264</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>222</v>
+        <v>263</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4237,13 +6726,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>224</v>
+        <v>265</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>215</v>
+        <v>256</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>222</v>
+        <v>263</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4251,17 +6740,17 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>225</v>
+        <v>266</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>213</v>
+        <v>254</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>222</v>
+        <v>263</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C18" s="5"/>
+      <c r="C18" s="11"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -4287,16 +6776,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>71</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>31</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4304,13 +6793,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>131</v>
+        <v>172</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>132</v>
+        <v>173</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>45</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4318,13 +6807,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>180</v>
+        <v>221</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>181</v>
+        <v>222</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>45</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4332,13 +6821,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>182</v>
+        <v>223</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>226</v>
+        <v>267</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>45</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -4367,16 +6856,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>71</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>31</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4384,13 +6873,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>227</v>
+        <v>268</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>189</v>
+        <v>230</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>198</v>
+        <v>239</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4398,13 +6887,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>228</v>
+        <v>269</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>191</v>
+        <v>232</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>198</v>
+        <v>239</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4412,13 +6901,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>229</v>
+        <v>270</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>132</v>
+        <v>173</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>198</v>
+        <v>239</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4426,13 +6915,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>230</v>
+        <v>271</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>209</v>
+        <v>250</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>198</v>
+        <v>239</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4440,13 +6929,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>231</v>
+        <v>272</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>185</v>
+        <v>226</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>198</v>
+        <v>239</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4454,13 +6943,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>232</v>
+        <v>273</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>187</v>
+        <v>228</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>198</v>
+        <v>239</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4468,13 +6957,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>233</v>
+        <v>274</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>194</v>
+        <v>235</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>198</v>
+        <v>239</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4482,26 +6971,26 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>234</v>
+        <v>275</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>196</v>
+        <v>237</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>198</v>
+        <v>239</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
+      <c r="A10" s="13"/>
+      <c r="B10" s="13"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="13"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
+      <c r="A11" s="13"/>
+      <c r="B11" s="13"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -4530,16 +7019,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>71</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>31</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4547,13 +7036,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>235</v>
+        <v>276</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>236</v>
+        <v>277</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>34</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4561,13 +7050,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>237</v>
+        <v>278</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>238</v>
+        <v>279</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>34</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4575,13 +7064,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>239</v>
+        <v>280</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>240</v>
+        <v>281</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>34</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4589,13 +7078,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>241</v>
+        <v>282</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>242</v>
+        <v>283</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>34</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -4625,16 +7114,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>71</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>31</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4642,13 +7131,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>243</v>
+        <v>284</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>244</v>
+        <v>285</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>245</v>
+        <v>286</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4656,13 +7145,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>243</v>
+        <v>284</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>244</v>
+        <v>285</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>245</v>
+        <v>286</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4670,13 +7159,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>246</v>
+        <v>287</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>247</v>
+        <v>288</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>245</v>
+        <v>286</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4684,13 +7173,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>246</v>
+        <v>287</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>247</v>
+        <v>288</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>245</v>
+        <v>286</v>
       </c>
     </row>
   </sheetData>
@@ -4719,13 +7208,13 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4733,10 +7222,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>248</v>
+        <v>289</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>88</v>
+        <v>129</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4744,10 +7233,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>249</v>
+        <v>290</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>86</v>
+        <v>127</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4755,10 +7244,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>250</v>
+        <v>291</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>84</v>
+        <v>125</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4766,10 +7255,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>251</v>
+        <v>292</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>82</v>
+        <v>123</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4777,10 +7266,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>252</v>
+        <v>293</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>80</v>
+        <v>121</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4788,10 +7277,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>253</v>
+        <v>294</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>78</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4799,10 +7288,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>254</v>
+        <v>295</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>76</v>
+        <v>117</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4810,10 +7299,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>255</v>
+        <v>296</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>74</v>
+        <v>115</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4821,10 +7310,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>256</v>
+        <v>297</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>257</v>
+        <v>298</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4832,10 +7321,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>258</v>
+        <v>299</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>259</v>
+        <v>300</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4845,7 +7334,7 @@
       <c r="A13" s="1"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C18" s="5"/>
+      <c r="C18" s="11"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -4873,13 +7362,13 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4887,10 +7376,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>260</v>
+        <v>301</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>88</v>
+        <v>129</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4898,10 +7387,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>261</v>
+        <v>302</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>86</v>
+        <v>127</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4909,10 +7398,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>262</v>
+        <v>303</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>84</v>
+        <v>125</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4920,10 +7409,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>263</v>
+        <v>304</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>82</v>
+        <v>123</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4931,10 +7420,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>264</v>
+        <v>305</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>80</v>
+        <v>121</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4942,10 +7431,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>265</v>
+        <v>306</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>78</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4953,10 +7442,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>266</v>
+        <v>307</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>76</v>
+        <v>117</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4964,10 +7453,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>267</v>
+        <v>308</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>74</v>
+        <v>115</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4975,10 +7464,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>268</v>
+        <v>309</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>269</v>
+        <v>310</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4986,10 +7475,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>270</v>
+        <v>311</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>271</v>
+        <v>312</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4999,7 +7488,7 @@
       <c r="A13" s="1"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C18" s="5"/>
+      <c r="C18" s="11"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -5026,16 +7515,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>71</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>31</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5043,13 +7532,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>48</v>
+        <v>89</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5057,13 +7546,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>48</v>
+        <v>89</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5071,13 +7560,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>51</v>
+        <v>92</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>52</v>
+        <v>93</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5085,13 +7574,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>53</v>
+        <v>94</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>54</v>
+        <v>95</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5099,13 +7588,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>55</v>
+        <v>96</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>56</v>
+        <v>97</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5113,13 +7602,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>57</v>
+        <v>98</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>58</v>
+        <v>99</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5127,13 +7616,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>59</v>
+        <v>100</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>60</v>
+        <v>101</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5141,13 +7630,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>61</v>
+        <v>102</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>62</v>
+        <v>103</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5155,13 +7644,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>63</v>
+        <v>104</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>64</v>
+        <v>105</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5169,13 +7658,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>65</v>
+        <v>106</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>66</v>
+        <v>107</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5183,13 +7672,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>67</v>
+        <v>108</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>68</v>
+        <v>109</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5197,13 +7686,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>69</v>
+        <v>110</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>70</v>
+        <v>111</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5211,13 +7700,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>71</v>
+        <v>112</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>72</v>
+        <v>113</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5225,13 +7714,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>71</v>
+        <v>112</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>72</v>
+        <v>113</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5239,13 +7728,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>73</v>
+        <v>114</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>74</v>
+        <v>115</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5253,13 +7742,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>75</v>
+        <v>116</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>76</v>
+        <v>117</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5267,13 +7756,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>77</v>
+        <v>118</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5281,13 +7770,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>79</v>
+        <v>120</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>80</v>
+        <v>121</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5295,13 +7784,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>81</v>
+        <v>122</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>82</v>
+        <v>123</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5309,13 +7798,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>83</v>
+        <v>124</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>84</v>
+        <v>125</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5323,13 +7812,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>85</v>
+        <v>126</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>86</v>
+        <v>127</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5337,13 +7826,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>87</v>
+        <v>128</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>88</v>
+        <v>129</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -5372,35 +7861,35 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>272</v>
+        <v>313</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>273</v>
+        <v>314</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>274</v>
+        <v>315</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>275</v>
+        <v>316</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>276</v>
+        <v>317</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>277</v>
+        <v>318</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>278</v>
+        <v>319</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>279</v>
+        <v>320</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5434,7 +7923,7 @@
       <c r="A13" s="1"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C18" s="5"/>
+      <c r="C18" s="11"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -5462,16 +7951,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>71</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>31</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5479,13 +7968,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>280</v>
+        <v>321</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>281</v>
+        <v>322</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>34</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5493,13 +7982,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>282</v>
+        <v>323</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>283</v>
+        <v>324</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>34</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5507,13 +7996,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>37</v>
+        <v>78</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>284</v>
+        <v>325</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>34</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5521,13 +8010,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>109</v>
+        <v>150</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>96</v>
+        <v>137</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>34</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5535,13 +8024,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>42</v>
+        <v>83</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>34</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -5564,15 +8053,15 @@
   <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="19.72"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16383" style="0" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16383" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>105</v>
+        <v>146</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5580,7 +8069,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>41</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5588,7 +8077,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>107</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5596,7 +8085,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>110</v>
+        <v>151</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5604,7 +8093,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>112</v>
+        <v>153</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5612,7 +8101,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>109</v>
+        <v>150</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5620,7 +8109,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>109</v>
+        <v>150</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5628,7 +8117,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>116</v>
+        <v>157</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5636,7 +8125,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>118</v>
+        <v>159</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5644,7 +8133,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>120</v>
+        <v>161</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5652,7 +8141,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>122</v>
+        <v>163</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5660,7 +8149,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>41</v>
+        <v>82</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5668,7 +8157,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>124</v>
+        <v>165</v>
       </c>
     </row>
   </sheetData>
@@ -5692,18 +8181,18 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="19.31"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="17.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="0" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>103</v>
+        <v>144</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>104</v>
+        <v>145</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5711,10 +8200,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>109</v>
+        <v>150</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>113</v>
+        <v>154</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5722,10 +8211,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>109</v>
+        <v>150</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>114</v>
+        <v>155</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5733,10 +8222,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>115</v>
+        <v>156</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>113</v>
+        <v>154</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5744,10 +8233,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>117</v>
+        <v>158</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>114</v>
+        <v>155</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5755,10 +8244,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>119</v>
+        <v>160</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>109</v>
+        <v>150</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5766,10 +8255,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>121</v>
+        <v>162</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>109</v>
+        <v>150</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5777,10 +8266,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>123</v>
+        <v>164</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5788,14 +8277,14 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>124</v>
+        <v>165</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>125</v>
+        <v>166</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C18" s="5"/>
+      <c r="C18" s="11"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -5818,18 +8307,18 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="17.78"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="19.72"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="0" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>104</v>
+        <v>145</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>285</v>
+        <v>326</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5837,10 +8326,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>113</v>
+        <v>154</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>109</v>
+        <v>150</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5848,10 +8337,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>114</v>
+        <v>155</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>109</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5859,10 +8348,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>113</v>
+        <v>154</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>115</v>
+        <v>156</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5870,10 +8359,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>114</v>
+        <v>155</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>117</v>
+        <v>158</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5881,10 +8370,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>109</v>
+        <v>150</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>119</v>
+        <v>160</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5892,10 +8381,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>109</v>
+        <v>150</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>121</v>
+        <v>162</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5903,10 +8392,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>123</v>
+        <v>164</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>41</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5914,14 +8403,14 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>125</v>
+        <v>166</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>124</v>
+        <v>165</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="5"/>
+      <c r="B18" s="11"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -5948,16 +8437,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>30</v>
+        <v>71</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>31</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5965,13 +8454,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>89</v>
+        <v>130</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>90</v>
+        <v>131</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5979,13 +8468,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>91</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5993,13 +8482,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>93</v>
+        <v>134</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>94</v>
+        <v>135</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6007,13 +8496,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>95</v>
+        <v>136</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>96</v>
+        <v>137</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -6040,26 +8529,26 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>97</v>
+        <v>138</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>98</v>
+        <v>139</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>99</v>
+        <v>140</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>100</v>
+        <v>141</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>102</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>
@@ -6088,16 +8577,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>103</v>
+        <v>144</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>104</v>
+        <v>145</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>105</v>
+        <v>146</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6105,13 +8594,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>41</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6119,13 +8608,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>106</v>
+        <v>147</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>107</v>
+        <v>148</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>107</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6133,13 +8622,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>108</v>
+        <v>149</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>109</v>
+        <v>150</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>110</v>
+        <v>151</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6147,13 +8636,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>111</v>
+        <v>152</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>109</v>
+        <v>150</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>112</v>
+        <v>153</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6161,13 +8650,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>109</v>
+        <v>150</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>113</v>
+        <v>154</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>109</v>
+        <v>150</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6175,13 +8664,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>109</v>
+        <v>150</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>114</v>
+        <v>155</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>109</v>
+        <v>150</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6189,13 +8678,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>115</v>
+        <v>156</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>113</v>
+        <v>154</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>116</v>
+        <v>157</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6203,13 +8692,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>117</v>
+        <v>158</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>114</v>
+        <v>155</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>118</v>
+        <v>159</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6217,13 +8706,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>119</v>
+        <v>160</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>109</v>
+        <v>150</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>120</v>
+        <v>161</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6231,13 +8720,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>121</v>
+        <v>162</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>109</v>
+        <v>150</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>122</v>
+        <v>163</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6245,13 +8734,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>123</v>
+        <v>164</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>41</v>
+        <v>82</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6259,17 +8748,17 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>124</v>
+        <v>165</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>125</v>
+        <v>166</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>124</v>
+        <v>165</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C18" s="5"/>
+      <c r="C18" s="11"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -6297,16 +8786,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>103</v>
+        <v>144</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>104</v>
+        <v>145</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>105</v>
+        <v>146</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6314,13 +8803,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>109</v>
+        <v>150</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>113</v>
+        <v>154</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>109</v>
+        <v>150</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6328,13 +8817,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>109</v>
+        <v>150</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>114</v>
+        <v>155</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>109</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6342,13 +8831,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>115</v>
+        <v>156</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>113</v>
+        <v>154</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>116</v>
+        <v>157</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6356,13 +8845,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>117</v>
+        <v>158</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>114</v>
+        <v>155</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>118</v>
+        <v>159</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6370,13 +8859,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>119</v>
+        <v>160</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>109</v>
+        <v>150</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>120</v>
+        <v>161</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6384,13 +8873,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>121</v>
+        <v>162</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>109</v>
+        <v>150</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>122</v>
+        <v>163</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6398,13 +8887,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>123</v>
+        <v>164</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>41</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6412,17 +8901,17 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>124</v>
+        <v>165</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>125</v>
+        <v>166</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>124</v>
+        <v>165</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C18" s="5"/>
+      <c r="C18" s="11"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -6450,16 +8939,16 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>69</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>103</v>
+        <v>144</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>104</v>
+        <v>145</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>105</v>
+        <v>146</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6467,13 +8956,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>109</v>
+        <v>150</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>113</v>
+        <v>154</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>109</v>
+        <v>150</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6481,13 +8970,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>109</v>
+        <v>150</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>114</v>
+        <v>155</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>109</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6495,13 +8984,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>115</v>
+        <v>156</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>113</v>
+        <v>154</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>116</v>
+        <v>157</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6509,13 +8998,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>117</v>
+        <v>158</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>114</v>
+        <v>155</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>118</v>
+        <v>159</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6523,13 +9012,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>119</v>
+        <v>160</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>109</v>
+        <v>150</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>120</v>
+        <v>161</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6537,13 +9026,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>121</v>
+        <v>162</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>109</v>
+        <v>150</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>122</v>
+        <v>163</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6551,13 +9040,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>123</v>
+        <v>164</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>41</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6565,17 +9054,17 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>124</v>
+        <v>165</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>125</v>
+        <v>166</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>124</v>
+        <v>165</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C18" s="5"/>
+      <c r="C18" s="11"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/Manual/source/CZ/tab/connectors.xlsx
+++ b/Manual/source/CZ/tab/connectors.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="52"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="17"/>
   </bookViews>
   <sheets>
     <sheet name="rozcestnik" sheetId="1" state="visible" r:id="rId3"/>
@@ -791,7 +791,7 @@
     <t xml:space="preserve">0,75 ~ 16 mm2</t>
   </si>
   <si>
-    <t xml:space="preserve">0,2 ~ 10 mm2</t>
+    <t xml:space="preserve">0,2 ~ 6 mm2</t>
   </si>
   <si>
     <t xml:space="preserve">-B2</t>
@@ -12127,152 +12127,112 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="19.31"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="49.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16383" style="0" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16383" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+      <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>400</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>402</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>404</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+      <c r="A5" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>404</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
+      <c r="A6" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="1" t="s">
         <v>400</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
+      <c r="A7" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" s="1" t="s">
         <v>402</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="n">
+      <c r="A8" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="C8" s="0" t="s">
+      <c r="C8" s="1" t="s">
         <v>406</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="n">
+      <c r="A9" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="C9" s="0" t="s">
+      <c r="C9" s="1" t="s">
         <v>408</v>
       </c>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="0"/>
-      <c r="C10" s="0"/>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="0"/>
-      <c r="C11" s="0"/>
-    </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="0"/>
-      <c r="C12" s="0"/>
-    </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="0"/>
-      <c r="C13" s="0"/>
-    </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="0"/>
-      <c r="C14" s="0"/>
-    </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="0"/>
-      <c r="C15" s="0"/>
-    </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="0"/>
-      <c r="C16" s="0"/>
-    </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="0"/>
-      <c r="C17" s="0"/>
-    </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="0"/>
-      <c r="C18" s="0"/>
-    </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="0"/>
-      <c r="C19" s="0"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -12295,7 +12255,7 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="19.31"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="23.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16383" style="0" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16383" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12316,7 +12276,7 @@
       <c r="B2" s="1" t="s">
         <v>409</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>410</v>
       </c>
     </row>
@@ -12327,7 +12287,7 @@
       <c r="B3" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>412</v>
       </c>
     </row>
@@ -12338,7 +12298,7 @@
       <c r="B4" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>413</v>
       </c>
     </row>
@@ -12349,7 +12309,7 @@
       <c r="B5" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>414</v>
       </c>
     </row>
@@ -12360,7 +12320,7 @@
       <c r="B6" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="1" t="s">
         <v>416</v>
       </c>
     </row>
@@ -12371,7 +12331,7 @@
       <c r="B7" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" s="1" t="s">
         <v>417</v>
       </c>
     </row>
@@ -12382,7 +12342,7 @@
       <c r="B8" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="C8" s="0" t="s">
+      <c r="C8" s="1" t="s">
         <v>418</v>
       </c>
     </row>
@@ -12393,7 +12353,7 @@
       <c r="B9" s="1" t="s">
         <v>409</v>
       </c>
-      <c r="C9" s="0" t="s">
+      <c r="C9" s="1" t="s">
         <v>419</v>
       </c>
     </row>
@@ -12404,7 +12364,7 @@
       <c r="B10" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="C10" s="0" t="s">
+      <c r="C10" s="1" t="s">
         <v>420</v>
       </c>
     </row>
@@ -12415,7 +12375,7 @@
       <c r="B11" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="C11" s="0" t="s">
+      <c r="C11" s="1" t="s">
         <v>421</v>
       </c>
     </row>
@@ -12449,115 +12409,113 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="9.73"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="29.25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16383" style="0" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16383" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+      <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>423</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>425</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>427</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+      <c r="A5" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>429</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
+      <c r="A6" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="1" t="s">
         <v>431</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
+      <c r="A7" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" s="1" t="s">
         <v>433</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="n">
+      <c r="A8" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="C8" s="0" t="s">
+      <c r="C8" s="1" t="s">
         <v>435</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="n">
+      <c r="A9" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="C9" s="0" t="s">
+      <c r="C9" s="1" t="s">
         <v>437</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1"/>
-      <c r="C10" s="0"/>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1"/>
-      <c r="C11" s="0"/>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1"/>
